--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_environmental_waste_services.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2094863807444144</v>
+        <v>0.2090178134306278</v>
       </c>
       <c r="C2">
-        <v>1.113170212469458</v>
+        <v>1.10531859200126</v>
       </c>
       <c r="D2">
-        <v>1.100170212469458</v>
+        <v>1.103328592001261</v>
       </c>
       <c r="E2">
-        <v>-0.041</v>
+        <v>-0.02999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.01101</v>
       </c>
       <c r="G2">
         <v>0.013</v>
@@ -1433,28 +1433,28 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.000553803</v>
       </c>
       <c r="N2">
-        <v>0.01466666666666667</v>
+        <v>0.01411286366666667</v>
       </c>
       <c r="O2">
-        <v>0.00352</v>
+        <v>0.00338708728</v>
       </c>
       <c r="P2">
-        <v>0.01114666666666667</v>
+        <v>0.01072577638666667</v>
       </c>
       <c r="Q2">
-        <v>0.01914666666666667</v>
+        <v>0.01872577638666667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2094863807444144</v>
+        <v>0.2107429630612402</v>
       </c>
       <c r="T2">
-        <v>0.8042521102410373</v>
+        <v>0.8104261668449079</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>26.4835449910287</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2090178134306278</v>
+        <v>0.2085492461168412</v>
       </c>
       <c r="C3">
-        <v>1.10531859200126</v>
+        <v>1.097485157957252</v>
       </c>
       <c r="D3">
-        <v>1.103328592001261</v>
+        <v>1.106505157957252</v>
       </c>
       <c r="E3">
-        <v>-0.02999</v>
+        <v>-0.01898</v>
       </c>
       <c r="F3">
-        <v>0.01101</v>
+        <v>0.02202</v>
       </c>
       <c r="G3">
         <v>0.013</v>
@@ -1515,28 +1515,28 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M3">
-        <v>0.000553803</v>
+        <v>0.001107606</v>
       </c>
       <c r="N3">
-        <v>0.01411286366666667</v>
+        <v>0.01355906066666667</v>
       </c>
       <c r="O3">
-        <v>0.00338708728</v>
+        <v>0.00325417456</v>
       </c>
       <c r="P3">
-        <v>0.01072577638666667</v>
+        <v>0.01030488610666667</v>
       </c>
       <c r="Q3">
-        <v>0.01872577638666667</v>
+        <v>0.01830488610666667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2107429630612402</v>
+        <v>0.2120251899151441</v>
       </c>
       <c r="T3">
-        <v>0.8104261668449079</v>
+        <v>0.8167262246039595</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>26.4835449910287</v>
+        <v>13.24177249551435</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2085492461168412</v>
+        <v>0.2081536388030546</v>
       </c>
       <c r="C4">
-        <v>1.097485157957252</v>
+        <v>1.089171380453142</v>
       </c>
       <c r="D4">
-        <v>1.106505157957252</v>
+        <v>1.109201380453142</v>
       </c>
       <c r="E4">
-        <v>-0.01898</v>
+        <v>-0.007970000000000005</v>
       </c>
       <c r="F4">
-        <v>0.02202</v>
+        <v>0.03303</v>
       </c>
       <c r="G4">
         <v>0.013</v>
@@ -1597,45 +1597,45 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M4">
-        <v>0.001107606</v>
+        <v>0.001767105</v>
       </c>
       <c r="N4">
-        <v>0.01355906066666667</v>
+        <v>0.01289956166666667</v>
       </c>
       <c r="O4">
-        <v>0.00325417456</v>
+        <v>0.0030958948</v>
       </c>
       <c r="P4">
-        <v>0.01030488610666667</v>
+        <v>0.009803666866666666</v>
       </c>
       <c r="Q4">
-        <v>0.01830488610666667</v>
+        <v>0.01780366686666667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2120251899151441</v>
+        <v>0.2133338544361388</v>
       </c>
       <c r="T4">
-        <v>0.8167262246039595</v>
+        <v>0.8231561804611359</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V4">
         <v>0.24</v>
       </c>
       <c r="W4">
-        <v>0.038228</v>
+        <v>0.04066</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y4">
-        <v>13.24177249551435</v>
+        <v>8.299827495630801</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2081536388030546</v>
+        <v>0.207733711489268</v>
       </c>
       <c r="C5">
-        <v>1.089171380453142</v>
+        <v>1.081037767042805</v>
       </c>
       <c r="D5">
-        <v>1.109201380453142</v>
+        <v>1.112077767042805</v>
       </c>
       <c r="E5">
-        <v>-0.007970000000000005</v>
+        <v>0.003040000000000001</v>
       </c>
       <c r="F5">
-        <v>0.03303</v>
+        <v>0.04404</v>
       </c>
       <c r="G5">
         <v>0.013</v>
@@ -1679,45 +1679,45 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M5">
-        <v>0.001767105</v>
+        <v>0.002391372</v>
       </c>
       <c r="N5">
-        <v>0.01289956166666667</v>
+        <v>0.01227529466666667</v>
       </c>
       <c r="O5">
-        <v>0.0030958948</v>
+        <v>0.00294607072</v>
       </c>
       <c r="P5">
-        <v>0.009803666866666666</v>
+        <v>0.009329223946666666</v>
       </c>
       <c r="Q5">
-        <v>0.01780366686666667</v>
+        <v>0.01732922394666667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2133338544361388</v>
+        <v>0.2146697828013209</v>
       </c>
       <c r="T5">
-        <v>0.8231561804611359</v>
+        <v>0.8297200937320035</v>
       </c>
       <c r="U5">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V5">
         <v>0.24</v>
       </c>
       <c r="W5">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y5">
-        <v>8.299827495630801</v>
+        <v>6.133159820666406</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.207733711489268</v>
+        <v>0.2073335441754814</v>
       </c>
       <c r="C6">
-        <v>1.081037767042805</v>
+        <v>1.07278271911812</v>
       </c>
       <c r="D6">
-        <v>1.112077767042805</v>
+        <v>1.11483271911812</v>
       </c>
       <c r="E6">
-        <v>0.003040000000000001</v>
+        <v>0.01405</v>
       </c>
       <c r="F6">
-        <v>0.04404</v>
+        <v>0.05505</v>
       </c>
       <c r="G6">
         <v>0.013</v>
@@ -1761,45 +1761,45 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M6">
-        <v>0.002391372</v>
+        <v>0.003044265</v>
       </c>
       <c r="N6">
-        <v>0.01227529466666667</v>
+        <v>0.01162240166666667</v>
       </c>
       <c r="O6">
-        <v>0.00294607072</v>
+        <v>0.0027893764</v>
       </c>
       <c r="P6">
-        <v>0.009329223946666666</v>
+        <v>0.008833025266666667</v>
       </c>
       <c r="Q6">
-        <v>0.01732922394666667</v>
+        <v>0.01683302526666667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2146697828013209</v>
+        <v>0.216033835974191</v>
       </c>
       <c r="T6">
-        <v>0.8297200937320035</v>
+        <v>0.8364221946506788</v>
       </c>
       <c r="U6">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V6">
         <v>0.24</v>
       </c>
       <c r="W6">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y6">
-        <v>6.133159820666406</v>
+        <v>4.81780221717448</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2073335441754814</v>
+        <v>0.2071765768616949</v>
       </c>
       <c r="C7">
-        <v>1.07278271911812</v>
+        <v>1.062857091464123</v>
       </c>
       <c r="D7">
-        <v>1.11483271911812</v>
+        <v>1.115917091464123</v>
       </c>
       <c r="E7">
-        <v>0.01405</v>
+        <v>0.02506000000000001</v>
       </c>
       <c r="F7">
-        <v>0.05505</v>
+        <v>0.06606000000000001</v>
       </c>
       <c r="G7">
         <v>0.013</v>
@@ -1843,45 +1843,45 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M7">
-        <v>0.003044265</v>
+        <v>0.004049478</v>
       </c>
       <c r="N7">
-        <v>0.01162240166666667</v>
+        <v>0.01061718866666667</v>
       </c>
       <c r="O7">
-        <v>0.0027893764</v>
+        <v>0.00254812528</v>
       </c>
       <c r="P7">
-        <v>0.008833025266666667</v>
+        <v>0.008069063386666665</v>
       </c>
       <c r="Q7">
-        <v>0.01683302526666667</v>
+        <v>0.01606906338666667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.216033835974191</v>
+        <v>0.2174269115549945</v>
       </c>
       <c r="T7">
-        <v>0.8364221946506788</v>
+        <v>0.8432668934612408</v>
       </c>
       <c r="U7">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V7">
         <v>0.24</v>
       </c>
       <c r="W7">
-        <v>0.042028</v>
+        <v>0.046588</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>4.81780221717448</v>
+        <v>3.621865995238563</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2071765768616949</v>
+        <v>0.2073555295479083</v>
       </c>
       <c r="C8">
-        <v>1.062857091464123</v>
+        <v>1.050611006498986</v>
       </c>
       <c r="D8">
-        <v>1.115917091464123</v>
+        <v>1.114681006498986</v>
       </c>
       <c r="E8">
-        <v>0.02505999999999999</v>
+        <v>0.03606999999999998</v>
       </c>
       <c r="F8">
-        <v>0.06605999999999999</v>
+        <v>0.07706999999999999</v>
       </c>
       <c r="G8">
         <v>0.013</v>
@@ -1925,45 +1925,45 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M8">
-        <v>0.004049478</v>
+        <v>0.005541332999999999</v>
       </c>
       <c r="N8">
-        <v>0.01061718866666667</v>
+        <v>0.009125333666666667</v>
       </c>
       <c r="O8">
-        <v>0.00254812528</v>
+        <v>0.00219008008</v>
       </c>
       <c r="P8">
-        <v>0.008069063386666665</v>
+        <v>0.006935253586666667</v>
       </c>
       <c r="Q8">
-        <v>0.01606906338666667</v>
+        <v>0.01493525358666667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2174269115549945</v>
+        <v>0.218849945750439</v>
       </c>
       <c r="T8">
-        <v>0.8432668934612408</v>
+        <v>0.8502587900956858</v>
       </c>
       <c r="U8">
-        <v>0.0613</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V8">
         <v>0.24</v>
       </c>
       <c r="W8">
-        <v>0.046588</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>3.621865995238563</v>
+        <v>2.646775905123671</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2073555295479082</v>
+        <v>0.2072882422341216</v>
       </c>
       <c r="C9">
-        <v>1.050611006498986</v>
+        <v>1.040065460688459</v>
       </c>
       <c r="D9">
-        <v>1.114681006498986</v>
+        <v>1.115145460688459</v>
       </c>
       <c r="E9">
-        <v>0.03607</v>
+        <v>0.04708</v>
       </c>
       <c r="F9">
-        <v>0.07707</v>
+        <v>0.08808000000000001</v>
       </c>
       <c r="G9">
         <v>0.013</v>
@@ -2007,45 +2007,45 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M9">
-        <v>0.005541333000000001</v>
+        <v>0.006676464000000001</v>
       </c>
       <c r="N9">
-        <v>0.009125333666666666</v>
+        <v>0.007990202666666665</v>
       </c>
       <c r="O9">
-        <v>0.00219008008</v>
+        <v>0.001917648639999999</v>
       </c>
       <c r="P9">
-        <v>0.006935253586666665</v>
+        <v>0.006072554026666665</v>
       </c>
       <c r="Q9">
-        <v>0.01493525358666667</v>
+        <v>0.01407255402666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.218849945750439</v>
+        <v>0.2203039154718713</v>
       </c>
       <c r="T9">
-        <v>0.8502587900956858</v>
+        <v>0.8574026844830536</v>
       </c>
       <c r="U9">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V9">
         <v>0.24</v>
       </c>
       <c r="W9">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y9">
-        <v>2.646775905123671</v>
+        <v>2.196771624420751</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2072882422341216</v>
+        <v>0.207984754920335</v>
       </c>
       <c r="C10">
-        <v>1.040065460688459</v>
+        <v>1.02426639798818</v>
       </c>
       <c r="D10">
-        <v>1.115145460688459</v>
+        <v>1.11035639798818</v>
       </c>
       <c r="E10">
-        <v>0.04708</v>
+        <v>0.05809</v>
       </c>
       <c r="F10">
-        <v>0.08808000000000001</v>
+        <v>0.09909</v>
       </c>
       <c r="G10">
         <v>0.013</v>
@@ -2089,45 +2089,45 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M10">
-        <v>0.006676464000000001</v>
+        <v>0.0089181</v>
       </c>
       <c r="N10">
-        <v>0.007990202666666665</v>
+        <v>0.005748566666666666</v>
       </c>
       <c r="O10">
-        <v>0.001917648639999999</v>
+        <v>0.001379656</v>
       </c>
       <c r="P10">
-        <v>0.006072554026666665</v>
+        <v>0.004368910666666666</v>
       </c>
       <c r="Q10">
-        <v>0.01407255402666667</v>
+        <v>0.01236891066666667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2203039154718713</v>
+        <v>0.2217898405717967</v>
       </c>
       <c r="T10">
-        <v>0.8574026844830536</v>
+        <v>0.8647035875382756</v>
       </c>
       <c r="U10">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V10">
         <v>0.24</v>
       </c>
       <c r="W10">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>2.196771624420751</v>
+        <v>1.644595448208325</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.207984754920335</v>
+        <v>0.2128244324770458</v>
       </c>
       <c r="C11">
-        <v>1.02426639798818</v>
+        <v>0.9810828599039715</v>
       </c>
       <c r="D11">
-        <v>1.11035639798818</v>
+        <v>1.078182859903972</v>
       </c>
       <c r="E11">
-        <v>0.05809</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="F11">
-        <v>0.09909</v>
+        <v>0.1101</v>
       </c>
       <c r="G11">
         <v>0.013</v>
@@ -2171,45 +2171,45 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M11">
-        <v>0.0089181</v>
+        <v>0.01616268</v>
       </c>
       <c r="N11">
-        <v>0.005748566666666666</v>
+        <v>-0.001496013333333332</v>
       </c>
       <c r="O11">
-        <v>0.001379656</v>
+        <v>-0.0003590431999999998</v>
       </c>
       <c r="P11">
-        <v>0.004368910666666666</v>
+        <v>-0.001136970133333333</v>
       </c>
       <c r="Q11">
-        <v>0.01236891066666667</v>
+        <v>0.00686302986666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2217898405717967</v>
+        <v>0.2237128066981808</v>
       </c>
       <c r="T11">
-        <v>0.8647035875382756</v>
+        <v>0.8741518358166787</v>
       </c>
       <c r="U11">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V11">
-        <v>0.24</v>
+        <v>0.2177856642586502</v>
       </c>
       <c r="W11">
-        <v>0.0684</v>
+        <v>0.1148290644868302</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y11">
-        <v>1.644595448208325</v>
+        <v>0.9074402677443758</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2128244324770458</v>
+        <v>0.2138344324770458</v>
       </c>
       <c r="C12">
-        <v>0.9810828599039715</v>
+        <v>0.9635922554680219</v>
       </c>
       <c r="D12">
-        <v>1.078182859903972</v>
+        <v>1.071702255468022</v>
       </c>
       <c r="E12">
-        <v>0.06909999999999999</v>
+        <v>0.08010999999999999</v>
       </c>
       <c r="F12">
-        <v>0.1101</v>
+        <v>0.12111</v>
       </c>
       <c r="G12">
         <v>0.013</v>
@@ -2253,37 +2253,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M12">
-        <v>0.01616268</v>
+        <v>0.017778948</v>
       </c>
       <c r="N12">
-        <v>-0.001496013333333336</v>
+        <v>-0.003112281333333333</v>
       </c>
       <c r="O12">
-        <v>-0.0003590432000000006</v>
+        <v>-0.0007469475199999998</v>
       </c>
       <c r="P12">
-        <v>-0.001136970133333335</v>
+        <v>-0.002365333813333333</v>
       </c>
       <c r="Q12">
-        <v>0.006863029866666667</v>
+        <v>0.005634666186666669</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2237128066981808</v>
+        <v>0.2257118269981604</v>
       </c>
       <c r="T12">
-        <v>0.8741518358166787</v>
+        <v>0.8839737665561918</v>
       </c>
       <c r="U12">
         <v>0.1468</v>
       </c>
       <c r="V12">
-        <v>0.2177856642586501</v>
+        <v>0.1979869675078638</v>
       </c>
       <c r="W12">
-        <v>0.1148290644868302</v>
+        <v>0.1177355131698456</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.9074402677443756</v>
+        <v>0.8249456979494325</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2138344324770458</v>
+        <v>0.2222831085461035</v>
       </c>
       <c r="C13">
-        <v>0.9635922554680219</v>
+        <v>0.901277259349583</v>
       </c>
       <c r="D13">
-        <v>1.071702255468022</v>
+        <v>1.020397259349583</v>
       </c>
       <c r="E13">
-        <v>0.08010999999999999</v>
+        <v>0.09111999999999998</v>
       </c>
       <c r="F13">
-        <v>0.12111</v>
+        <v>0.13212</v>
       </c>
       <c r="G13">
         <v>0.013</v>
@@ -2335,45 +2335,45 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M13">
-        <v>0.017778948</v>
+        <v>0.026529696</v>
       </c>
       <c r="N13">
-        <v>-0.003112281333333333</v>
+        <v>-0.01186302933333333</v>
       </c>
       <c r="O13">
-        <v>-0.0007469475199999998</v>
+        <v>-0.002847127039999999</v>
       </c>
       <c r="P13">
-        <v>-0.002365333813333333</v>
+        <v>-0.009015902293333333</v>
       </c>
       <c r="Q13">
-        <v>0.005634666186666669</v>
+        <v>-0.001015902293333331</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2257118269981604</v>
+        <v>0.2288456842016142</v>
       </c>
       <c r="T13">
-        <v>0.8839737665561918</v>
+        <v>0.8993715733719417</v>
       </c>
       <c r="U13">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V13">
-        <v>0.1979869675078638</v>
+        <v>0.1326815052837394</v>
       </c>
       <c r="W13">
-        <v>0.1177355131698456</v>
+        <v>0.1741575537390251</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y13">
-        <v>0.8249456979494325</v>
+        <v>0.5528396053489142</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2222831085461035</v>
+        <v>0.2238331085461035</v>
       </c>
       <c r="C14">
-        <v>0.901277259349583</v>
+        <v>0.8813834300163312</v>
       </c>
       <c r="D14">
-        <v>1.020397259349583</v>
+        <v>1.011513430016331</v>
       </c>
       <c r="E14">
-        <v>0.09111999999999998</v>
+        <v>0.10213</v>
       </c>
       <c r="F14">
-        <v>0.13212</v>
+        <v>0.14313</v>
       </c>
       <c r="G14">
         <v>0.013</v>
@@ -2417,37 +2417,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M14">
-        <v>0.026529696</v>
+        <v>0.028740504</v>
       </c>
       <c r="N14">
-        <v>-0.01186302933333333</v>
+        <v>-0.01407383733333334</v>
       </c>
       <c r="O14">
-        <v>-0.002847127039999999</v>
+        <v>-0.003377720960000001</v>
       </c>
       <c r="P14">
-        <v>-0.009015902293333333</v>
+        <v>-0.01069611637333334</v>
       </c>
       <c r="Q14">
-        <v>-0.001015902293333331</v>
+        <v>-0.002696116373333335</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2288456842016142</v>
+        <v>0.2309496575832419</v>
       </c>
       <c r="T14">
-        <v>0.8993715733719417</v>
+        <v>0.9097091776635733</v>
       </c>
       <c r="U14">
         <v>0.2008</v>
       </c>
       <c r="V14">
-        <v>0.1326815052837394</v>
+        <v>0.1224752356465287</v>
       </c>
       <c r="W14">
-        <v>0.1741575537390251</v>
+        <v>0.1762069726821771</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.5528396053489142</v>
+        <v>0.5103134818605362</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2238331085461035</v>
+        <v>0.2306699459194911</v>
       </c>
       <c r="C15">
-        <v>0.8813834300163312</v>
+        <v>0.83296576600895</v>
       </c>
       <c r="D15">
-        <v>1.011513430016331</v>
+        <v>0.97410576600895</v>
       </c>
       <c r="E15">
-        <v>0.10213</v>
+        <v>0.11314</v>
       </c>
       <c r="F15">
-        <v>0.14313</v>
+        <v>0.15414</v>
       </c>
       <c r="G15">
         <v>0.013</v>
@@ -2499,45 +2499,45 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M15">
-        <v>0.028740504</v>
+        <v>0.036346212</v>
       </c>
       <c r="N15">
-        <v>-0.01407383733333334</v>
+        <v>-0.02167954533333333</v>
       </c>
       <c r="O15">
-        <v>-0.003377720960000001</v>
+        <v>-0.00520309088</v>
       </c>
       <c r="P15">
-        <v>-0.01069611637333334</v>
+        <v>-0.01647645445333333</v>
       </c>
       <c r="Q15">
-        <v>-0.002696116373333335</v>
+        <v>-0.008476454453333332</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2309496575832419</v>
+        <v>0.2335523714776838</v>
       </c>
       <c r="T15">
-        <v>0.9097091776635733</v>
+        <v>0.9224972797184838</v>
       </c>
       <c r="U15">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.1224752356465287</v>
+        <v>0.0968464058923114</v>
       </c>
       <c r="W15">
-        <v>0.1762069726821771</v>
+        <v>0.212963617490593</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y15">
-        <v>0.5103134818605362</v>
+        <v>0.4035266912179643</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2306699459194911</v>
+        <v>0.232569945919491</v>
       </c>
       <c r="C16">
-        <v>0.83296576600895</v>
+        <v>0.8120462436481372</v>
       </c>
       <c r="D16">
-        <v>0.97410576600895</v>
+        <v>0.9641962436481372</v>
       </c>
       <c r="E16">
-        <v>0.11314</v>
+        <v>0.12415</v>
       </c>
       <c r="F16">
-        <v>0.15414</v>
+        <v>0.16515</v>
       </c>
       <c r="G16">
         <v>0.013</v>
@@ -2581,37 +2581,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M16">
-        <v>0.036346212</v>
+        <v>0.03894237</v>
       </c>
       <c r="N16">
-        <v>-0.02167954533333333</v>
+        <v>-0.02427570333333334</v>
       </c>
       <c r="O16">
-        <v>-0.00520309088</v>
+        <v>-0.005826168800000001</v>
       </c>
       <c r="P16">
-        <v>-0.01647645445333333</v>
+        <v>-0.01844953453333334</v>
       </c>
       <c r="Q16">
-        <v>-0.008476454453333332</v>
+        <v>-0.01044953453333333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2335523714776838</v>
+        <v>0.235761222906833</v>
       </c>
       <c r="T16">
-        <v>0.9224972797184838</v>
+        <v>0.9333501888916425</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.0968464058923114</v>
+        <v>0.09038997883282399</v>
       </c>
       <c r="W16">
-        <v>0.212963617490593</v>
+        <v>0.2144860429912201</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.4035266912179643</v>
+        <v>0.3766249118034333</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.232569945919491</v>
+        <v>0.234469945919491</v>
       </c>
       <c r="C17">
-        <v>0.8120462436481374</v>
+        <v>0.7913263089046716</v>
       </c>
       <c r="D17">
-        <v>0.9641962436481374</v>
+        <v>0.9544863089046716</v>
       </c>
       <c r="E17">
-        <v>0.12415</v>
+        <v>0.13516</v>
       </c>
       <c r="F17">
-        <v>0.16515</v>
+        <v>0.17616</v>
       </c>
       <c r="G17">
         <v>0.013</v>
@@ -2663,37 +2663,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M17">
-        <v>0.03894237</v>
+        <v>0.04153852800000001</v>
       </c>
       <c r="N17">
-        <v>-0.02427570333333333</v>
+        <v>-0.02687186133333334</v>
       </c>
       <c r="O17">
-        <v>-0.005826168799999999</v>
+        <v>-0.00644924672</v>
       </c>
       <c r="P17">
-        <v>-0.01844953453333333</v>
+        <v>-0.02042261461333334</v>
       </c>
       <c r="Q17">
-        <v>-0.01044953453333333</v>
+        <v>-0.01242261461333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.235761222906833</v>
+        <v>0.2380226660366762</v>
       </c>
       <c r="T17">
-        <v>0.9333501888916425</v>
+        <v>0.9444615006641619</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.090389978832824</v>
+        <v>0.08474060515577249</v>
       </c>
       <c r="W17">
-        <v>0.2144860429912201</v>
+        <v>0.2158181653042688</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.3766249118034334</v>
+        <v>0.3530858548157187</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.234469945919491</v>
+        <v>0.236369945919491</v>
       </c>
       <c r="C18">
-        <v>0.7913263089046716</v>
+        <v>0.7707999920574966</v>
       </c>
       <c r="D18">
-        <v>0.9544863089046716</v>
+        <v>0.9449699920574967</v>
       </c>
       <c r="E18">
-        <v>0.13516</v>
+        <v>0.14617</v>
       </c>
       <c r="F18">
-        <v>0.17616</v>
+        <v>0.18717</v>
       </c>
       <c r="G18">
         <v>0.013</v>
@@ -2745,37 +2745,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M18">
-        <v>0.04153852800000001</v>
+        <v>0.044134686</v>
       </c>
       <c r="N18">
-        <v>-0.02687186133333334</v>
+        <v>-0.02946801933333333</v>
       </c>
       <c r="O18">
-        <v>-0.00644924672</v>
+        <v>-0.007072324639999999</v>
       </c>
       <c r="P18">
-        <v>-0.02042261461333334</v>
+        <v>-0.02239569469333333</v>
       </c>
       <c r="Q18">
-        <v>-0.01242261461333334</v>
+        <v>-0.01439569469333333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2380226660366762</v>
+        <v>0.2403386017720578</v>
       </c>
       <c r="T18">
-        <v>0.9444615006641619</v>
+        <v>0.9558405548890314</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.08474060515577249</v>
+        <v>0.07975586367602117</v>
       </c>
       <c r="W18">
-        <v>0.2158181653042688</v>
+        <v>0.2169935673451942</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.3530858548157187</v>
+        <v>0.3323160986500883</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.236369945919491</v>
+        <v>0.238269945919491</v>
       </c>
       <c r="C19">
-        <v>0.7707999920574966</v>
+        <v>0.7504615591100469</v>
       </c>
       <c r="D19">
-        <v>0.9449699920574967</v>
+        <v>0.9356415591100469</v>
       </c>
       <c r="E19">
-        <v>0.14617</v>
+        <v>0.15718</v>
       </c>
       <c r="F19">
-        <v>0.18717</v>
+        <v>0.19818</v>
       </c>
       <c r="G19">
         <v>0.013</v>
@@ -2827,37 +2827,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M19">
-        <v>0.044134686</v>
+        <v>0.04673084400000001</v>
       </c>
       <c r="N19">
-        <v>-0.02946801933333333</v>
+        <v>-0.03206417733333334</v>
       </c>
       <c r="O19">
-        <v>-0.007072324639999999</v>
+        <v>-0.007695402560000001</v>
       </c>
       <c r="P19">
-        <v>-0.02239569469333333</v>
+        <v>-0.02436877477333334</v>
       </c>
       <c r="Q19">
-        <v>-0.01439569469333333</v>
+        <v>-0.01636877477333334</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2403386017720578</v>
+        <v>0.2427110237448878</v>
       </c>
       <c r="T19">
-        <v>0.9558405548890314</v>
+        <v>0.9674971470218244</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.07975586367602117</v>
+        <v>0.07532498236068663</v>
       </c>
       <c r="W19">
-        <v>0.2169935673451942</v>
+        <v>0.2180383691593501</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.3323160986500883</v>
+        <v>0.3138540931695277</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.238269945919491</v>
+        <v>0.240169945919491</v>
       </c>
       <c r="C20">
-        <v>0.7504615591100469</v>
+        <v>0.7303055002690086</v>
       </c>
       <c r="D20">
-        <v>0.9356415591100469</v>
+        <v>0.9264955002690086</v>
       </c>
       <c r="E20">
-        <v>0.15718</v>
+        <v>0.16819</v>
       </c>
       <c r="F20">
-        <v>0.19818</v>
+        <v>0.20919</v>
       </c>
       <c r="G20">
         <v>0.013</v>
@@ -2909,37 +2909,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M20">
-        <v>0.046730844</v>
+        <v>0.049327002</v>
       </c>
       <c r="N20">
-        <v>-0.03206417733333333</v>
+        <v>-0.03466033533333333</v>
       </c>
       <c r="O20">
-        <v>-0.007695402559999999</v>
+        <v>-0.008318480479999999</v>
       </c>
       <c r="P20">
-        <v>-0.02436877477333333</v>
+        <v>-0.02634185485333333</v>
       </c>
       <c r="Q20">
-        <v>-0.01636877477333333</v>
+        <v>-0.01834185485333333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2427110237448878</v>
+        <v>0.2451420240380346</v>
       </c>
       <c r="T20">
-        <v>0.9674971470218244</v>
+        <v>0.9794415562443161</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.07532498236068665</v>
+        <v>0.07136050960486104</v>
       </c>
       <c r="W20">
-        <v>0.2180383691593501</v>
+        <v>0.2189731918351738</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3138540931695277</v>
+        <v>0.2973354566869211</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.240169945919491</v>
+        <v>0.242069945919491</v>
       </c>
       <c r="C21">
-        <v>0.7303055002690086</v>
+        <v>0.7103265190922714</v>
       </c>
       <c r="D21">
-        <v>0.9264955002690086</v>
+        <v>0.9175265190922715</v>
       </c>
       <c r="E21">
-        <v>0.16819</v>
+        <v>0.1792</v>
       </c>
       <c r="F21">
-        <v>0.20919</v>
+        <v>0.2202</v>
       </c>
       <c r="G21">
         <v>0.013</v>
@@ -2991,37 +2991,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M21">
-        <v>0.049327002</v>
+        <v>0.05192316</v>
       </c>
       <c r="N21">
-        <v>-0.03466033533333333</v>
+        <v>-0.03725649333333333</v>
       </c>
       <c r="O21">
-        <v>-0.008318480479999999</v>
+        <v>-0.008941558400000001</v>
       </c>
       <c r="P21">
-        <v>-0.02634185485333333</v>
+        <v>-0.02831493493333333</v>
       </c>
       <c r="Q21">
-        <v>-0.01834185485333333</v>
+        <v>-0.02031493493333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2451420240380346</v>
+        <v>0.24763379933851</v>
       </c>
       <c r="T21">
-        <v>0.9794415562443161</v>
+        <v>0.99168457569737</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.07136050960486104</v>
+        <v>0.06779248412461798</v>
       </c>
       <c r="W21">
-        <v>0.2189731918351738</v>
+        <v>0.2198145322434151</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.2973354566869211</v>
+        <v>0.282468683852575</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.242069945919491</v>
+        <v>0.243969945919491</v>
       </c>
       <c r="C22">
-        <v>0.7103265190922714</v>
+        <v>0.6905195222611599</v>
       </c>
       <c r="D22">
-        <v>0.9175265190922715</v>
+        <v>0.9087295222611599</v>
       </c>
       <c r="E22">
-        <v>0.1792</v>
+        <v>0.19021</v>
       </c>
       <c r="F22">
-        <v>0.2202</v>
+        <v>0.23121</v>
       </c>
       <c r="G22">
         <v>0.013</v>
@@ -3073,37 +3073,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M22">
-        <v>0.05192316</v>
+        <v>0.05451931800000001</v>
       </c>
       <c r="N22">
-        <v>-0.03725649333333333</v>
+        <v>-0.03985265133333334</v>
       </c>
       <c r="O22">
-        <v>-0.008941558400000001</v>
+        <v>-0.009564636320000002</v>
       </c>
       <c r="P22">
-        <v>-0.02831493493333333</v>
+        <v>-0.03028801501333334</v>
       </c>
       <c r="Q22">
-        <v>-0.02031493493333333</v>
+        <v>-0.02228801501333334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.24763379933851</v>
+        <v>0.2501886575579848</v>
       </c>
       <c r="T22">
-        <v>0.99168457569737</v>
+        <v>1.004237545009995</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.06779248412461798</v>
+        <v>0.06456427059487427</v>
       </c>
       <c r="W22">
-        <v>0.2198145322434151</v>
+        <v>0.2205757449937287</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.282468683852575</v>
+        <v>0.2690177941453095</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.243969945919491</v>
+        <v>0.245869945919491</v>
       </c>
       <c r="C23">
-        <v>0.6905195222611601</v>
+        <v>0.6708796099354428</v>
       </c>
       <c r="D23">
-        <v>0.9087295222611601</v>
+        <v>0.9000996099354428</v>
       </c>
       <c r="E23">
-        <v>0.19021</v>
+        <v>0.20122</v>
       </c>
       <c r="F23">
-        <v>0.23121</v>
+        <v>0.24222</v>
       </c>
       <c r="G23">
         <v>0.013</v>
@@ -3155,37 +3155,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M23">
-        <v>0.054519318</v>
+        <v>0.057115476</v>
       </c>
       <c r="N23">
-        <v>-0.03985265133333334</v>
+        <v>-0.04244880933333333</v>
       </c>
       <c r="O23">
-        <v>-0.00956463632</v>
+        <v>-0.01018771424</v>
       </c>
       <c r="P23">
-        <v>-0.03028801501333334</v>
+        <v>-0.03226109509333333</v>
       </c>
       <c r="Q23">
-        <v>-0.02228801501333334</v>
+        <v>-0.02426109509333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2501886575579848</v>
+        <v>0.2528090249625743</v>
       </c>
       <c r="T23">
-        <v>1.004237545009995</v>
+        <v>1.017112385330636</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.06456427059487427</v>
+        <v>0.06162953102237999</v>
       </c>
       <c r="W23">
-        <v>0.2205757449937287</v>
+        <v>0.2212677565849228</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.2690177941453095</v>
+        <v>0.25678971259325</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.245869945919491</v>
+        <v>0.2477699459194911</v>
       </c>
       <c r="C24">
-        <v>0.6708796099354428</v>
+        <v>0.6514020666527451</v>
       </c>
       <c r="D24">
-        <v>0.9000996099354428</v>
+        <v>0.8916320666527452</v>
       </c>
       <c r="E24">
-        <v>0.20122</v>
+        <v>0.21223</v>
       </c>
       <c r="F24">
-        <v>0.24222</v>
+        <v>0.25323</v>
       </c>
       <c r="G24">
         <v>0.013</v>
@@ -3237,37 +3237,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M24">
-        <v>0.057115476</v>
+        <v>0.05971163400000001</v>
       </c>
       <c r="N24">
-        <v>-0.04244880933333333</v>
+        <v>-0.04504496733333334</v>
       </c>
       <c r="O24">
-        <v>-0.01018771424</v>
+        <v>-0.01081079216</v>
       </c>
       <c r="P24">
-        <v>-0.03226109509333333</v>
+        <v>-0.03423417517333334</v>
       </c>
       <c r="Q24">
-        <v>-0.02426109509333333</v>
+        <v>-0.02623417517333334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2528090249625743</v>
+        <v>0.2554974538581922</v>
       </c>
       <c r="T24">
-        <v>1.017112385330636</v>
+        <v>1.030321637088177</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.06162953102237999</v>
+        <v>0.05894998619531998</v>
       </c>
       <c r="W24">
-        <v>0.2212677565849228</v>
+        <v>0.2218995932551436</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.25678971259325</v>
+        <v>0.2456249424804999</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2477699459194911</v>
+        <v>0.249669945919491</v>
       </c>
       <c r="C25">
-        <v>0.6514020666527451</v>
+        <v>0.632082352736849</v>
       </c>
       <c r="D25">
-        <v>0.8916320666527452</v>
+        <v>0.883322352736849</v>
       </c>
       <c r="E25">
-        <v>0.21223</v>
+        <v>0.22324</v>
       </c>
       <c r="F25">
-        <v>0.25323</v>
+        <v>0.26424</v>
       </c>
       <c r="G25">
         <v>0.013</v>
@@ -3319,37 +3319,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M25">
-        <v>0.05971163400000001</v>
+        <v>0.06230779200000001</v>
       </c>
       <c r="N25">
-        <v>-0.04504496733333334</v>
+        <v>-0.04764112533333334</v>
       </c>
       <c r="O25">
-        <v>-0.01081079216</v>
+        <v>-0.01143387008</v>
       </c>
       <c r="P25">
-        <v>-0.03423417517333334</v>
+        <v>-0.03620725525333333</v>
       </c>
       <c r="Q25">
-        <v>-0.02623417517333334</v>
+        <v>-0.02820725525333333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2554974538581922</v>
+        <v>0.2582566308826421</v>
       </c>
       <c r="T25">
-        <v>1.030321637088177</v>
+        <v>1.043878500734074</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.05894998619531998</v>
+        <v>0.05649373677051498</v>
       </c>
       <c r="W25">
-        <v>0.2218995932551436</v>
+        <v>0.2224787768695126</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2456249424804999</v>
+        <v>0.2353905698771458</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.249669945919491</v>
+        <v>0.251569945919491</v>
       </c>
       <c r="C26">
-        <v>0.6320823527368491</v>
+        <v>0.6129160961819844</v>
       </c>
       <c r="D26">
-        <v>0.883322352736849</v>
+        <v>0.8751660961819844</v>
       </c>
       <c r="E26">
-        <v>0.22324</v>
+        <v>0.23425</v>
       </c>
       <c r="F26">
-        <v>0.26424</v>
+        <v>0.27525</v>
       </c>
       <c r="G26">
         <v>0.013</v>
@@ -3401,37 +3401,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M26">
-        <v>0.06230779199999999</v>
+        <v>0.06490395</v>
       </c>
       <c r="N26">
-        <v>-0.04764112533333333</v>
+        <v>-0.05023728333333333</v>
       </c>
       <c r="O26">
-        <v>-0.01143387008</v>
+        <v>-0.012056948</v>
       </c>
       <c r="P26">
-        <v>-0.03620725525333333</v>
+        <v>-0.03818033533333334</v>
       </c>
       <c r="Q26">
-        <v>-0.02820725525333333</v>
+        <v>-0.03018033533333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2582566308826421</v>
+        <v>0.2610893859610773</v>
       </c>
       <c r="T26">
-        <v>1.043878500734074</v>
+        <v>1.057796880743861</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.05649373677051499</v>
+        <v>0.05423398729969439</v>
       </c>
       <c r="W26">
-        <v>0.2224787768695126</v>
+        <v>0.2230116257947321</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2353905698771459</v>
+        <v>0.22597494708206</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.251569945919491</v>
+        <v>0.253469945919491</v>
       </c>
       <c r="C27">
-        <v>0.6129160961819844</v>
+        <v>0.5938990849826342</v>
       </c>
       <c r="D27">
-        <v>0.8751660961819844</v>
+        <v>0.8671590849826343</v>
       </c>
       <c r="E27">
-        <v>0.23425</v>
+        <v>0.24526</v>
       </c>
       <c r="F27">
-        <v>0.27525</v>
+        <v>0.28626</v>
       </c>
       <c r="G27">
         <v>0.013</v>
@@ -3483,37 +3483,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M27">
-        <v>0.06490395</v>
+        <v>0.067500108</v>
       </c>
       <c r="N27">
-        <v>-0.05023728333333333</v>
+        <v>-0.05283344133333333</v>
       </c>
       <c r="O27">
-        <v>-0.012056948</v>
+        <v>-0.01268002592</v>
       </c>
       <c r="P27">
-        <v>-0.03818033533333334</v>
+        <v>-0.04015341541333334</v>
       </c>
       <c r="Q27">
-        <v>-0.03018033533333334</v>
+        <v>-0.03215341541333334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2610893859610773</v>
+        <v>0.2639987019875784</v>
       </c>
       <c r="T27">
-        <v>1.057796880743861</v>
+        <v>1.072091433186346</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.05423398729969439</v>
+        <v>0.05214806471124461</v>
       </c>
       <c r="W27">
-        <v>0.2230116257947321</v>
+        <v>0.2235034863410885</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.22597494708206</v>
+        <v>0.2172836029635192</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.253469945919491</v>
+        <v>0.255369945919491</v>
       </c>
       <c r="C28">
-        <v>0.5938990849826342</v>
+        <v>0.5750272598805752</v>
       </c>
       <c r="D28">
-        <v>0.8671590849826343</v>
+        <v>0.8592972598805753</v>
       </c>
       <c r="E28">
-        <v>0.24526</v>
+        <v>0.2562700000000001</v>
       </c>
       <c r="F28">
-        <v>0.28626</v>
+        <v>0.29727</v>
       </c>
       <c r="G28">
         <v>0.013</v>
@@ -3565,37 +3565,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M28">
-        <v>0.067500108</v>
+        <v>0.070096266</v>
       </c>
       <c r="N28">
-        <v>-0.05283344133333333</v>
+        <v>-0.05542959933333334</v>
       </c>
       <c r="O28">
-        <v>-0.01268002592</v>
+        <v>-0.01330310384</v>
       </c>
       <c r="P28">
-        <v>-0.04015341541333334</v>
+        <v>-0.04212649549333333</v>
       </c>
       <c r="Q28">
-        <v>-0.03215341541333334</v>
+        <v>-0.03412649549333333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2639987019875784</v>
+        <v>0.2669877253024767</v>
       </c>
       <c r="T28">
-        <v>1.072091433186346</v>
+        <v>1.086777617202597</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.05214806471124461</v>
+        <v>0.05021665490712444</v>
       </c>
       <c r="W28">
-        <v>0.2235034863410885</v>
+        <v>0.2239589127729001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2172836029635192</v>
+        <v>0.2092360621130185</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.255369945919491</v>
+        <v>0.257269945919491</v>
       </c>
       <c r="C29">
-        <v>0.5750272598805752</v>
+        <v>0.5562967075029118</v>
       </c>
       <c r="D29">
-        <v>0.8592972598805753</v>
+        <v>0.8515767075029118</v>
       </c>
       <c r="E29">
-        <v>0.2562700000000001</v>
+        <v>0.26728</v>
       </c>
       <c r="F29">
-        <v>0.29727</v>
+        <v>0.30828</v>
       </c>
       <c r="G29">
         <v>0.013</v>
@@ -3647,37 +3647,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M29">
-        <v>0.070096266</v>
+        <v>0.07269242400000001</v>
       </c>
       <c r="N29">
-        <v>-0.05542959933333334</v>
+        <v>-0.05802575733333334</v>
       </c>
       <c r="O29">
-        <v>-0.01330310384</v>
+        <v>-0.01392618176</v>
       </c>
       <c r="P29">
-        <v>-0.04212649549333333</v>
+        <v>-0.04409957557333334</v>
       </c>
       <c r="Q29">
-        <v>-0.03412649549333333</v>
+        <v>-0.03609957557333334</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2669877253024767</v>
+        <v>0.2700597770427889</v>
       </c>
       <c r="T29">
-        <v>1.086777617202597</v>
+        <v>1.101871750774856</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.05021665490712444</v>
+        <v>0.0484232029461557</v>
       </c>
       <c r="W29">
-        <v>0.2239589127729001</v>
+        <v>0.2243818087452965</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2092360621130185</v>
+        <v>0.2017633456089821</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.257269945919491</v>
+        <v>0.2591699459194911</v>
       </c>
       <c r="C30">
-        <v>0.5562967075029118</v>
+        <v>0.5377036538667355</v>
       </c>
       <c r="D30">
-        <v>0.8515767075029118</v>
+        <v>0.8439936538667354</v>
       </c>
       <c r="E30">
-        <v>0.26728</v>
+        <v>0.27829</v>
       </c>
       <c r="F30">
-        <v>0.30828</v>
+        <v>0.31929</v>
       </c>
       <c r="G30">
         <v>0.013</v>
@@ -3729,37 +3729,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M30">
-        <v>0.07269242400000001</v>
+        <v>0.07528858200000001</v>
       </c>
       <c r="N30">
-        <v>-0.05802575733333334</v>
+        <v>-0.06062191533333334</v>
       </c>
       <c r="O30">
-        <v>-0.01392618176</v>
+        <v>-0.01454925968</v>
       </c>
       <c r="P30">
-        <v>-0.04409957557333334</v>
+        <v>-0.04607265565333334</v>
       </c>
       <c r="Q30">
-        <v>-0.03609957557333334</v>
+        <v>-0.03807265565333334</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2700597770427889</v>
+        <v>0.2732183654518423</v>
       </c>
       <c r="T30">
-        <v>1.101871750774856</v>
+        <v>1.117391071208304</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.0484232029461557</v>
+        <v>0.04675343732732275</v>
       </c>
       <c r="W30">
-        <v>0.2243818087452965</v>
+        <v>0.2247755394782173</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2017633456089821</v>
+        <v>0.1948059888638448</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2591699459194911</v>
+        <v>0.261069945919491</v>
       </c>
       <c r="C31">
-        <v>0.5377036538667355</v>
+        <v>0.5192444582277562</v>
       </c>
       <c r="D31">
-        <v>0.8439936538667354</v>
+        <v>0.8365444582277561</v>
       </c>
       <c r="E31">
-        <v>0.27829</v>
+        <v>0.2893</v>
       </c>
       <c r="F31">
-        <v>0.31929</v>
+        <v>0.3303</v>
       </c>
       <c r="G31">
         <v>0.013</v>
@@ -3811,37 +3811,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M31">
-        <v>0.07528858199999999</v>
+        <v>0.07788473999999999</v>
       </c>
       <c r="N31">
-        <v>-0.06062191533333332</v>
+        <v>-0.06321807333333333</v>
       </c>
       <c r="O31">
-        <v>-0.01454925968</v>
+        <v>-0.0151723376</v>
       </c>
       <c r="P31">
-        <v>-0.04607265565333333</v>
+        <v>-0.04804573573333333</v>
       </c>
       <c r="Q31">
-        <v>-0.03807265565333333</v>
+        <v>-0.04004573573333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2732183654518423</v>
+        <v>0.2764671992440114</v>
       </c>
       <c r="T31">
-        <v>1.117391071208304</v>
+        <v>1.133353800796994</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.04675343732732275</v>
+        <v>0.045194989416412</v>
       </c>
       <c r="W31">
-        <v>0.2247755394782173</v>
+        <v>0.2251430214956101</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1948059888638448</v>
+        <v>0.1883124559017166</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.261069945919491</v>
+        <v>0.2629699459194911</v>
       </c>
       <c r="C32">
-        <v>0.5192444582277562</v>
+        <v>0.5009156072518388</v>
       </c>
       <c r="D32">
-        <v>0.8365444582277561</v>
+        <v>0.8292256072518388</v>
       </c>
       <c r="E32">
-        <v>0.2893</v>
+        <v>0.30031</v>
       </c>
       <c r="F32">
-        <v>0.3303</v>
+        <v>0.34131</v>
       </c>
       <c r="G32">
         <v>0.013</v>
@@ -3893,37 +3893,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M32">
-        <v>0.07788473999999999</v>
+        <v>0.08048089800000001</v>
       </c>
       <c r="N32">
-        <v>-0.06321807333333333</v>
+        <v>-0.06581423133333335</v>
       </c>
       <c r="O32">
-        <v>-0.0151723376</v>
+        <v>-0.01579541552</v>
       </c>
       <c r="P32">
-        <v>-0.04804573573333333</v>
+        <v>-0.05001881581333335</v>
       </c>
       <c r="Q32">
-        <v>-0.04004573573333333</v>
+        <v>-0.04201881581333335</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2764671992440114</v>
+        <v>0.2798102021316058</v>
       </c>
       <c r="T32">
-        <v>1.133353800796994</v>
+        <v>1.149779218199849</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.045194989416412</v>
+        <v>0.0437370865320116</v>
       </c>
       <c r="W32">
-        <v>0.2251430214956101</v>
+        <v>0.2254867949957517</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1883124559017166</v>
+        <v>0.1822378605500483</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2629699459194911</v>
+        <v>0.264869945919491</v>
       </c>
       <c r="C33">
-        <v>0.5009156072518388</v>
+        <v>0.4827137094898454</v>
       </c>
       <c r="D33">
-        <v>0.8292256072518388</v>
+        <v>0.8220337094898454</v>
       </c>
       <c r="E33">
-        <v>0.30031</v>
+        <v>0.31132</v>
       </c>
       <c r="F33">
-        <v>0.34131</v>
+        <v>0.35232</v>
       </c>
       <c r="G33">
         <v>0.013</v>
@@ -3975,37 +3975,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M33">
-        <v>0.08048089800000001</v>
+        <v>0.08307705600000001</v>
       </c>
       <c r="N33">
-        <v>-0.06581423133333335</v>
+        <v>-0.06841038933333335</v>
       </c>
       <c r="O33">
-        <v>-0.01579541552</v>
+        <v>-0.01641849344</v>
       </c>
       <c r="P33">
-        <v>-0.05001881581333335</v>
+        <v>-0.05199189589333335</v>
       </c>
       <c r="Q33">
-        <v>-0.04201881581333335</v>
+        <v>-0.04399189589333335</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2798102021316058</v>
+        <v>0.2832515286335411</v>
       </c>
       <c r="T33">
-        <v>1.149779218199849</v>
+        <v>1.166687736114553</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.0437370865320116</v>
+        <v>0.04237030257788624</v>
       </c>
       <c r="W33">
-        <v>0.2254867949957517</v>
+        <v>0.2258090826521345</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1822378605500483</v>
+        <v>0.1765429274078593</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.264869945919491</v>
+        <v>0.266769945919491</v>
       </c>
       <c r="C34">
-        <v>0.4827137094898454</v>
+        <v>0.4646354901375188</v>
       </c>
       <c r="D34">
-        <v>0.8220337094898454</v>
+        <v>0.8149654901375187</v>
       </c>
       <c r="E34">
-        <v>0.31132</v>
+        <v>0.32233</v>
       </c>
       <c r="F34">
-        <v>0.35232</v>
+        <v>0.36333</v>
       </c>
       <c r="G34">
         <v>0.013</v>
@@ -4057,37 +4057,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M34">
-        <v>0.08307705600000001</v>
+        <v>0.085673214</v>
       </c>
       <c r="N34">
-        <v>-0.06841038933333335</v>
+        <v>-0.07100654733333334</v>
       </c>
       <c r="O34">
-        <v>-0.01641849344</v>
+        <v>-0.01704157136</v>
       </c>
       <c r="P34">
-        <v>-0.05199189589333335</v>
+        <v>-0.05396497597333334</v>
       </c>
       <c r="Q34">
-        <v>-0.04399189589333335</v>
+        <v>-0.04596497597333334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2832515286335411</v>
+        <v>0.2867955812997134</v>
       </c>
       <c r="T34">
-        <v>1.166687736114553</v>
+        <v>1.184100985907308</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.04237030257788624</v>
+        <v>0.04108635401491999</v>
       </c>
       <c r="W34">
-        <v>0.2258090826521345</v>
+        <v>0.2261118377232819</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1765429274078593</v>
+        <v>0.1711931417288333</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.266769945919491</v>
+        <v>0.268669945919491</v>
       </c>
       <c r="C35">
-        <v>0.4646354901375188</v>
+        <v>0.4466777860634098</v>
       </c>
       <c r="D35">
-        <v>0.8149654901375187</v>
+        <v>0.8080177860634098</v>
       </c>
       <c r="E35">
-        <v>0.32233</v>
+        <v>0.33334</v>
       </c>
       <c r="F35">
-        <v>0.36333</v>
+        <v>0.37434</v>
       </c>
       <c r="G35">
         <v>0.013</v>
@@ -4139,37 +4139,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M35">
-        <v>0.085673214</v>
+        <v>0.088269372</v>
       </c>
       <c r="N35">
-        <v>-0.07100654733333334</v>
+        <v>-0.07360270533333334</v>
       </c>
       <c r="O35">
-        <v>-0.01704157136</v>
+        <v>-0.01766464928</v>
       </c>
       <c r="P35">
-        <v>-0.05396497597333334</v>
+        <v>-0.05593805605333334</v>
       </c>
       <c r="Q35">
-        <v>-0.04596497597333334</v>
+        <v>-0.04793805605333334</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2867955812997134</v>
+        <v>0.2904470295012243</v>
       </c>
       <c r="T35">
-        <v>1.184100985907308</v>
+        <v>1.202041909936206</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.04108635401491999</v>
+        <v>0.03987793183801058</v>
       </c>
       <c r="W35">
-        <v>0.2261118377232819</v>
+        <v>0.2263967836725971</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1711931417288333</v>
+        <v>0.1661580493250441</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.268669945919491</v>
+        <v>0.270569945919491</v>
       </c>
       <c r="C36">
-        <v>0.4466777860634098</v>
+        <v>0.4288375410889754</v>
       </c>
       <c r="D36">
-        <v>0.8080177860634098</v>
+        <v>0.8011875410889754</v>
       </c>
       <c r="E36">
-        <v>0.33334</v>
+        <v>0.34435</v>
       </c>
       <c r="F36">
-        <v>0.37434</v>
+        <v>0.38535</v>
       </c>
       <c r="G36">
         <v>0.013</v>
@@ -4221,37 +4221,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M36">
-        <v>0.088269372</v>
+        <v>0.09086553000000001</v>
       </c>
       <c r="N36">
-        <v>-0.07360270533333334</v>
+        <v>-0.07619886333333335</v>
       </c>
       <c r="O36">
-        <v>-0.01766464928</v>
+        <v>-0.0182877272</v>
       </c>
       <c r="P36">
-        <v>-0.05593805605333334</v>
+        <v>-0.05791113613333335</v>
       </c>
       <c r="Q36">
-        <v>-0.04793805605333334</v>
+        <v>-0.04991113613333335</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2904470295012243</v>
+        <v>0.2942108299550893</v>
       </c>
       <c r="T36">
-        <v>1.202041909936206</v>
+        <v>1.220534862396763</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.03987793183801058</v>
+        <v>0.03873856235692456</v>
       </c>
       <c r="W36">
-        <v>0.2263967836725971</v>
+        <v>0.2266654469962372</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1661580493250441</v>
+        <v>0.1614106764871857</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.270569945919491</v>
+        <v>0.272469945919491</v>
       </c>
       <c r="C37">
-        <v>0.4288375410889754</v>
+        <v>0.4111118015060589</v>
       </c>
       <c r="D37">
-        <v>0.8011875410889754</v>
+        <v>0.7944718015060589</v>
       </c>
       <c r="E37">
-        <v>0.34435</v>
+        <v>0.3553600000000001</v>
       </c>
       <c r="F37">
-        <v>0.38535</v>
+        <v>0.39636</v>
       </c>
       <c r="G37">
         <v>0.013</v>
@@ -4303,37 +4303,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M37">
-        <v>0.09086553000000001</v>
+        <v>0.09346168800000001</v>
       </c>
       <c r="N37">
-        <v>-0.07619886333333335</v>
+        <v>-0.07879502133333335</v>
       </c>
       <c r="O37">
-        <v>-0.0182877272</v>
+        <v>-0.01891080512000001</v>
       </c>
       <c r="P37">
-        <v>-0.05791113613333335</v>
+        <v>-0.05988421621333335</v>
       </c>
       <c r="Q37">
-        <v>-0.04991113613333335</v>
+        <v>-0.05188421621333335</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2942108299550893</v>
+        <v>0.2980922491731375</v>
       </c>
       <c r="T37">
-        <v>1.220534862396763</v>
+        <v>1.239605719621713</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.03873856235692456</v>
+        <v>0.03766249118034332</v>
       </c>
       <c r="W37">
-        <v>0.2266654469962372</v>
+        <v>0.2269191845796751</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1614106764871857</v>
+        <v>0.1569270465847638</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.272469945919491</v>
+        <v>0.274369945919491</v>
       </c>
       <c r="C38">
-        <v>0.4111118015060589</v>
+        <v>0.3934977118179368</v>
       </c>
       <c r="D38">
-        <v>0.7944718015060589</v>
+        <v>0.7878677118179368</v>
       </c>
       <c r="E38">
-        <v>0.35536</v>
+        <v>0.36637</v>
       </c>
       <c r="F38">
-        <v>0.39636</v>
+        <v>0.40737</v>
       </c>
       <c r="G38">
         <v>0.013</v>
@@ -4385,37 +4385,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M38">
-        <v>0.093461688</v>
+        <v>0.096057846</v>
       </c>
       <c r="N38">
-        <v>-0.07879502133333334</v>
+        <v>-0.08139117933333334</v>
       </c>
       <c r="O38">
-        <v>-0.01891080512</v>
+        <v>-0.01953388304</v>
       </c>
       <c r="P38">
-        <v>-0.05988421621333334</v>
+        <v>-0.06185729629333334</v>
       </c>
       <c r="Q38">
-        <v>-0.05188421621333334</v>
+        <v>-0.05385729629333334</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2980922491731375</v>
+        <v>0.3020968880489017</v>
       </c>
       <c r="T38">
-        <v>1.239605719621713</v>
+        <v>1.259282000885549</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.03766249118034332</v>
+        <v>0.03664458601330702</v>
       </c>
       <c r="W38">
-        <v>0.2269191845796751</v>
+        <v>0.2271592066180622</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1569270465847639</v>
+        <v>0.1526857750554459</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.274369945919491</v>
+        <v>0.2762699459194911</v>
       </c>
       <c r="C39">
-        <v>0.3934977118179368</v>
+        <v>0.3759925106910316</v>
       </c>
       <c r="D39">
-        <v>0.7878677118179368</v>
+        <v>0.7813725106910315</v>
       </c>
       <c r="E39">
-        <v>0.36637</v>
+        <v>0.37738</v>
       </c>
       <c r="F39">
-        <v>0.40737</v>
+        <v>0.41838</v>
       </c>
       <c r="G39">
         <v>0.013</v>
@@ -4467,37 +4467,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M39">
-        <v>0.096057846</v>
+        <v>0.098654004</v>
       </c>
       <c r="N39">
-        <v>-0.08139117933333334</v>
+        <v>-0.08398733733333334</v>
       </c>
       <c r="O39">
-        <v>-0.01953388304</v>
+        <v>-0.02015696096</v>
       </c>
       <c r="P39">
-        <v>-0.06185729629333334</v>
+        <v>-0.06383037637333334</v>
       </c>
       <c r="Q39">
-        <v>-0.05385729629333334</v>
+        <v>-0.05583037637333334</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.3020968880489017</v>
+        <v>0.3062307088238839</v>
       </c>
       <c r="T39">
-        <v>1.259282000885549</v>
+        <v>1.279593000899832</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03664458601330702</v>
+        <v>0.03568025480243052</v>
       </c>
       <c r="W39">
-        <v>0.2271592066180622</v>
+        <v>0.2273865959175869</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1526857750554459</v>
+        <v>0.1486677283434604</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2762699459194911</v>
+        <v>0.278169945919491</v>
       </c>
       <c r="C40">
-        <v>0.3759925106910316</v>
+        <v>0.3585935271052312</v>
       </c>
       <c r="D40">
-        <v>0.7813725106910315</v>
+        <v>0.7749835271052312</v>
       </c>
       <c r="E40">
-        <v>0.37738</v>
+        <v>0.38839</v>
       </c>
       <c r="F40">
-        <v>0.41838</v>
+        <v>0.42939</v>
       </c>
       <c r="G40">
         <v>0.013</v>
@@ -4549,37 +4549,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M40">
-        <v>0.098654004</v>
+        <v>0.101250162</v>
       </c>
       <c r="N40">
-        <v>-0.08398733733333334</v>
+        <v>-0.08658349533333334</v>
       </c>
       <c r="O40">
-        <v>-0.02015696096</v>
+        <v>-0.02078003888</v>
       </c>
       <c r="P40">
-        <v>-0.06383037637333334</v>
+        <v>-0.06580345645333334</v>
       </c>
       <c r="Q40">
-        <v>-0.05583037637333334</v>
+        <v>-0.05780345645333334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3062307088238839</v>
+        <v>0.3105000647062426</v>
       </c>
       <c r="T40">
-        <v>1.279593000899832</v>
+        <v>1.300569935340813</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03568025480243052</v>
+        <v>0.03476537647416307</v>
       </c>
       <c r="W40">
-        <v>0.2273865959175869</v>
+        <v>0.2276023242273923</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1486677283434604</v>
+        <v>0.1448557353090127</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.278169945919491</v>
+        <v>0.2800699459194911</v>
       </c>
       <c r="C41">
-        <v>0.3585935271052312</v>
+        <v>0.3412981766915422</v>
       </c>
       <c r="D41">
-        <v>0.7749835271052312</v>
+        <v>0.7686981766915422</v>
       </c>
       <c r="E41">
-        <v>0.38839</v>
+        <v>0.3994</v>
       </c>
       <c r="F41">
-        <v>0.42939</v>
+        <v>0.4404</v>
       </c>
       <c r="G41">
         <v>0.013</v>
@@ -4631,37 +4631,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M41">
-        <v>0.101250162</v>
+        <v>0.10384632</v>
       </c>
       <c r="N41">
-        <v>-0.08658349533333334</v>
+        <v>-0.08917965333333334</v>
       </c>
       <c r="O41">
-        <v>-0.02078003888</v>
+        <v>-0.0214031168</v>
       </c>
       <c r="P41">
-        <v>-0.06580345645333334</v>
+        <v>-0.06777653653333335</v>
       </c>
       <c r="Q41">
-        <v>-0.05780345645333334</v>
+        <v>-0.05977653653333335</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3105000647062426</v>
+        <v>0.3149117324513467</v>
       </c>
       <c r="T41">
-        <v>1.300569935340813</v>
+        <v>1.322246100929827</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.03476537647416307</v>
+        <v>0.03389624206230899</v>
       </c>
       <c r="W41">
-        <v>0.2276023242273923</v>
+        <v>0.2278072661217075</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1448557353090127</v>
+        <v>0.1412343419262875</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2800699459194911</v>
+        <v>0.281969945919491</v>
       </c>
       <c r="C42">
-        <v>0.3412981766915422</v>
+        <v>0.3241039582465257</v>
       </c>
       <c r="D42">
-        <v>0.7686981766915422</v>
+        <v>0.7625139582465257</v>
       </c>
       <c r="E42">
-        <v>0.3994</v>
+        <v>0.4104100000000001</v>
       </c>
       <c r="F42">
-        <v>0.4404</v>
+        <v>0.45141</v>
       </c>
       <c r="G42">
         <v>0.013</v>
@@ -4713,37 +4713,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M42">
-        <v>0.10384632</v>
+        <v>0.106442478</v>
       </c>
       <c r="N42">
-        <v>-0.08917965333333334</v>
+        <v>-0.09177581133333335</v>
       </c>
       <c r="O42">
-        <v>-0.0214031168</v>
+        <v>-0.02202619472</v>
       </c>
       <c r="P42">
-        <v>-0.06777653653333335</v>
+        <v>-0.06974961661333334</v>
       </c>
       <c r="Q42">
-        <v>-0.05977653653333335</v>
+        <v>-0.06174961661333334</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3149117324513467</v>
+        <v>0.3194729482556068</v>
       </c>
       <c r="T42">
-        <v>1.322246100929827</v>
+        <v>1.344657051793044</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.03389624206230899</v>
+        <v>0.03306950445103317</v>
       </c>
       <c r="W42">
-        <v>0.2278072661217075</v>
+        <v>0.2280022108504464</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1412343419262875</v>
+        <v>0.1377896018793048</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.281969945919491</v>
+        <v>0.2838699459194911</v>
       </c>
       <c r="C43">
-        <v>0.3241039582465257</v>
+        <v>0.307008450413637</v>
       </c>
       <c r="D43">
-        <v>0.7625139582465257</v>
+        <v>0.756428450413637</v>
       </c>
       <c r="E43">
-        <v>0.4104100000000001</v>
+        <v>0.4214200000000001</v>
       </c>
       <c r="F43">
-        <v>0.45141</v>
+        <v>0.4624200000000001</v>
       </c>
       <c r="G43">
         <v>0.013</v>
@@ -4795,37 +4795,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M43">
-        <v>0.106442478</v>
+        <v>0.109038636</v>
       </c>
       <c r="N43">
-        <v>-0.09177581133333335</v>
+        <v>-0.09437196933333336</v>
       </c>
       <c r="O43">
-        <v>-0.02202619472</v>
+        <v>-0.02264927264000001</v>
       </c>
       <c r="P43">
-        <v>-0.06974961661333334</v>
+        <v>-0.07172269669333335</v>
       </c>
       <c r="Q43">
-        <v>-0.06174961661333334</v>
+        <v>-0.06372269669333334</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3194729482556068</v>
+        <v>0.3241914473634621</v>
       </c>
       <c r="T43">
-        <v>1.344657051793044</v>
+        <v>1.367840794065338</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03306950445103317</v>
+        <v>0.03228213529743713</v>
       </c>
       <c r="W43">
-        <v>0.2280022108504464</v>
+        <v>0.2281878724968643</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1377896018793048</v>
+        <v>0.1345088970726547</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2838699459194911</v>
+        <v>0.285769945919491</v>
       </c>
       <c r="C44">
-        <v>0.3070084504136371</v>
+        <v>0.2900093085222268</v>
       </c>
       <c r="D44">
-        <v>0.756428450413637</v>
+        <v>0.7504393085222267</v>
       </c>
       <c r="E44">
-        <v>0.42142</v>
+        <v>0.43243</v>
       </c>
       <c r="F44">
-        <v>0.46242</v>
+        <v>0.47343</v>
       </c>
       <c r="G44">
         <v>0.013</v>
@@ -4877,37 +4877,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M44">
-        <v>0.109038636</v>
+        <v>0.111634794</v>
       </c>
       <c r="N44">
-        <v>-0.09437196933333335</v>
+        <v>-0.09696812733333333</v>
       </c>
       <c r="O44">
-        <v>-0.02264927264</v>
+        <v>-0.02327235056</v>
       </c>
       <c r="P44">
-        <v>-0.07172269669333334</v>
+        <v>-0.07369577677333333</v>
       </c>
       <c r="Q44">
-        <v>-0.06372269669333333</v>
+        <v>-0.06569577677333333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3241914473634621</v>
+        <v>0.3290755078435228</v>
       </c>
       <c r="T44">
-        <v>1.367840794065338</v>
+        <v>1.391838000978765</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03228213529743713</v>
+        <v>0.0315313879649386</v>
       </c>
       <c r="W44">
-        <v>0.2281878724968643</v>
+        <v>0.2283648987178675</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1345088970726547</v>
+        <v>0.1313807831872441</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.285769945919491</v>
+        <v>0.2876699459194911</v>
       </c>
       <c r="C45">
-        <v>0.2900093085222268</v>
+        <v>0.2731042615755223</v>
       </c>
       <c r="D45">
-        <v>0.7504393085222267</v>
+        <v>0.7445442615755222</v>
       </c>
       <c r="E45">
-        <v>0.43243</v>
+        <v>0.44344</v>
       </c>
       <c r="F45">
-        <v>0.47343</v>
+        <v>0.48444</v>
       </c>
       <c r="G45">
         <v>0.013</v>
@@ -4959,37 +4959,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M45">
-        <v>0.111634794</v>
+        <v>0.114230952</v>
       </c>
       <c r="N45">
-        <v>-0.09696812733333333</v>
+        <v>-0.09956428533333334</v>
       </c>
       <c r="O45">
-        <v>-0.02327235056</v>
+        <v>-0.02389542848</v>
       </c>
       <c r="P45">
-        <v>-0.07369577677333333</v>
+        <v>-0.07566885685333333</v>
       </c>
       <c r="Q45">
-        <v>-0.06569577677333333</v>
+        <v>-0.06766885685333332</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3290755078435228</v>
+        <v>0.3341339990550143</v>
       </c>
       <c r="T45">
-        <v>1.391838000978765</v>
+        <v>1.416692250996243</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.0315313879649386</v>
+        <v>0.03081476551118999</v>
       </c>
       <c r="W45">
-        <v>0.2283648987178675</v>
+        <v>0.2285338782924614</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1313807831872441</v>
+        <v>0.1283948562966249</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2876699459194911</v>
+        <v>0.289569945919491</v>
       </c>
       <c r="C46">
-        <v>0.2731042615755223</v>
+        <v>0.2562911093794732</v>
       </c>
       <c r="D46">
-        <v>0.7445442615755222</v>
+        <v>0.7387411093794732</v>
       </c>
       <c r="E46">
-        <v>0.44344</v>
+        <v>0.45445</v>
       </c>
       <c r="F46">
-        <v>0.48444</v>
+        <v>0.49545</v>
       </c>
       <c r="G46">
         <v>0.013</v>
@@ -5041,37 +5041,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M46">
-        <v>0.114230952</v>
+        <v>0.11682711</v>
       </c>
       <c r="N46">
-        <v>-0.09956428533333334</v>
+        <v>-0.1021604433333334</v>
       </c>
       <c r="O46">
-        <v>-0.02389542848</v>
+        <v>-0.0245185064</v>
       </c>
       <c r="P46">
-        <v>-0.07566885685333333</v>
+        <v>-0.07764193693333335</v>
       </c>
       <c r="Q46">
-        <v>-0.06766885685333332</v>
+        <v>-0.06964193693333334</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3341339990550143</v>
+        <v>0.3393764354014691</v>
       </c>
       <c r="T46">
-        <v>1.416692250996243</v>
+        <v>1.442450291923447</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03081476551118999</v>
+        <v>0.03012999294427466</v>
       </c>
       <c r="W46">
-        <v>0.2285338782924614</v>
+        <v>0.2286953476637401</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1283948562966249</v>
+        <v>0.1255416372678111</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.289569945919491</v>
+        <v>0.291469945919491</v>
       </c>
       <c r="C47">
-        <v>0.2562911093794732</v>
+        <v>0.2395677198048242</v>
       </c>
       <c r="D47">
-        <v>0.7387411093794732</v>
+        <v>0.7330277198048242</v>
       </c>
       <c r="E47">
-        <v>0.45445</v>
+        <v>0.46546</v>
       </c>
       <c r="F47">
-        <v>0.49545</v>
+        <v>0.50646</v>
       </c>
       <c r="G47">
         <v>0.013</v>
@@ -5123,37 +5123,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M47">
-        <v>0.11682711</v>
+        <v>0.119423268</v>
       </c>
       <c r="N47">
-        <v>-0.1021604433333334</v>
+        <v>-0.1047566013333334</v>
       </c>
       <c r="O47">
-        <v>-0.0245185064</v>
+        <v>-0.02514158432</v>
       </c>
       <c r="P47">
-        <v>-0.07764193693333335</v>
+        <v>-0.07961501701333334</v>
       </c>
       <c r="Q47">
-        <v>-0.06964193693333334</v>
+        <v>-0.07161501701333334</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3393764354014691</v>
+        <v>0.3448130360570519</v>
       </c>
       <c r="T47">
-        <v>1.442450291923447</v>
+        <v>1.469162334366474</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03012999294427466</v>
+        <v>0.02947499309765999</v>
       </c>
       <c r="W47">
-        <v>0.2286953476637401</v>
+        <v>0.2288497966275718</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1255416372678111</v>
+        <v>0.12281247124025</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.291469945919491</v>
+        <v>0.2933699459194911</v>
       </c>
       <c r="C48">
-        <v>0.2395677198048242</v>
+        <v>0.2229320261752666</v>
       </c>
       <c r="D48">
-        <v>0.7330277198048242</v>
+        <v>0.7274020261752666</v>
       </c>
       <c r="E48">
-        <v>0.46546</v>
+        <v>0.47647</v>
       </c>
       <c r="F48">
-        <v>0.50646</v>
+        <v>0.51747</v>
       </c>
       <c r="G48">
         <v>0.013</v>
@@ -5205,37 +5205,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M48">
-        <v>0.119423268</v>
+        <v>0.122019426</v>
       </c>
       <c r="N48">
-        <v>-0.1047566013333334</v>
+        <v>-0.1073527593333333</v>
       </c>
       <c r="O48">
-        <v>-0.02514158432</v>
+        <v>-0.02576466224</v>
       </c>
       <c r="P48">
-        <v>-0.07961501701333334</v>
+        <v>-0.08158809709333334</v>
       </c>
       <c r="Q48">
-        <v>-0.07161501701333334</v>
+        <v>-0.07358809709333333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3448130360570519</v>
+        <v>0.3504547914543548</v>
       </c>
       <c r="T48">
-        <v>1.469162334366474</v>
+        <v>1.496882378411125</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02947499309765999</v>
+        <v>0.02884786558494382</v>
       </c>
       <c r="W48">
-        <v>0.2288497966275718</v>
+        <v>0.2289976732950703</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.12281247124025</v>
+        <v>0.1201994399372659</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2933699459194911</v>
+        <v>0.2952699459194911</v>
       </c>
       <c r="C49">
-        <v>0.2229320261752666</v>
+        <v>0.2063820247749414</v>
       </c>
       <c r="D49">
-        <v>0.7274020261752666</v>
+        <v>0.7218620247749414</v>
       </c>
       <c r="E49">
-        <v>0.47647</v>
+        <v>0.4874800000000001</v>
       </c>
       <c r="F49">
-        <v>0.51747</v>
+        <v>0.5284800000000001</v>
       </c>
       <c r="G49">
         <v>0.013</v>
@@ -5287,37 +5287,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M49">
-        <v>0.122019426</v>
+        <v>0.124615584</v>
       </c>
       <c r="N49">
-        <v>-0.1073527593333333</v>
+        <v>-0.1099489173333334</v>
       </c>
       <c r="O49">
-        <v>-0.02576466224</v>
+        <v>-0.02638774016</v>
       </c>
       <c r="P49">
-        <v>-0.08158809709333334</v>
+        <v>-0.08356117717333335</v>
       </c>
       <c r="Q49">
-        <v>-0.07358809709333333</v>
+        <v>-0.07556117717333334</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3504547914543548</v>
+        <v>0.3563135374438616</v>
       </c>
       <c r="T49">
-        <v>1.496882378411125</v>
+        <v>1.525668577995954</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02884786558494382</v>
+        <v>0.02824686838525749</v>
       </c>
       <c r="W49">
-        <v>0.2289976732950703</v>
+        <v>0.2291393884347563</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1201994399372659</v>
+        <v>0.1176952849385728</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.295269945919491</v>
+        <v>0.297169945919491</v>
       </c>
       <c r="C50">
-        <v>0.2063820247749417</v>
+        <v>0.1899157724689812</v>
       </c>
       <c r="D50">
-        <v>0.7218620247749417</v>
+        <v>0.7164057724689812</v>
       </c>
       <c r="E50">
-        <v>0.48748</v>
+        <v>0.49849</v>
       </c>
       <c r="F50">
-        <v>0.5284799999999999</v>
+        <v>0.53949</v>
       </c>
       <c r="G50">
         <v>0.013</v>
@@ -5369,37 +5369,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M50">
-        <v>0.124615584</v>
+        <v>0.127211742</v>
       </c>
       <c r="N50">
-        <v>-0.1099489173333333</v>
+        <v>-0.1125450753333334</v>
       </c>
       <c r="O50">
-        <v>-0.02638774016</v>
+        <v>-0.02701081808000001</v>
       </c>
       <c r="P50">
-        <v>-0.08356117717333333</v>
+        <v>-0.08553425725333336</v>
       </c>
       <c r="Q50">
-        <v>-0.07556117717333333</v>
+        <v>-0.07753425725333335</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3563135374438616</v>
+        <v>0.3624020381780549</v>
       </c>
       <c r="T50">
-        <v>1.525668577995954</v>
+        <v>1.555583648152737</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0282468683852575</v>
+        <v>0.02767040168351755</v>
       </c>
       <c r="W50">
-        <v>0.2291393884347563</v>
+        <v>0.2292753192830266</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1176952849385728</v>
+        <v>0.1152933403479898</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.297169945919491</v>
+        <v>0.299069945919491</v>
       </c>
       <c r="C51">
-        <v>0.1899157724689812</v>
+        <v>0.1735313844311531</v>
       </c>
       <c r="D51">
-        <v>0.7164057724689812</v>
+        <v>0.7110313844311531</v>
       </c>
       <c r="E51">
-        <v>0.49849</v>
+        <v>0.5095</v>
       </c>
       <c r="F51">
-        <v>0.53949</v>
+        <v>0.5505</v>
       </c>
       <c r="G51">
         <v>0.013</v>
@@ -5451,37 +5451,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M51">
-        <v>0.127211742</v>
+        <v>0.1298079</v>
       </c>
       <c r="N51">
-        <v>-0.1125450753333334</v>
+        <v>-0.1151412333333333</v>
       </c>
       <c r="O51">
-        <v>-0.02701081808000001</v>
+        <v>-0.027633896</v>
       </c>
       <c r="P51">
-        <v>-0.08553425725333336</v>
+        <v>-0.08750733733333334</v>
       </c>
       <c r="Q51">
-        <v>-0.07753425725333335</v>
+        <v>-0.07950733733333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3624020381780549</v>
+        <v>0.368734078941616</v>
       </c>
       <c r="T51">
-        <v>1.555583648152737</v>
+        <v>1.586695321115792</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02767040168351755</v>
+        <v>0.0271169936498472</v>
       </c>
       <c r="W51">
-        <v>0.2292753192830266</v>
+        <v>0.229405812897366</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1152933403479898</v>
+        <v>0.1129874735410299</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.299069945919491</v>
+        <v>0.3009699459194911</v>
       </c>
       <c r="C52">
-        <v>0.1735313844311531</v>
+        <v>0.1572270319730252</v>
       </c>
       <c r="D52">
-        <v>0.7110313844311531</v>
+        <v>0.7057370319730252</v>
       </c>
       <c r="E52">
-        <v>0.5095</v>
+        <v>0.5205099999999999</v>
       </c>
       <c r="F52">
-        <v>0.5505</v>
+        <v>0.56151</v>
       </c>
       <c r="G52">
         <v>0.013</v>
@@ -5533,37 +5533,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M52">
-        <v>0.1298079</v>
+        <v>0.132404058</v>
       </c>
       <c r="N52">
-        <v>-0.1151412333333333</v>
+        <v>-0.1177373913333333</v>
       </c>
       <c r="O52">
-        <v>-0.027633896</v>
+        <v>-0.02825697392</v>
       </c>
       <c r="P52">
-        <v>-0.08750733733333334</v>
+        <v>-0.08948041741333333</v>
       </c>
       <c r="Q52">
-        <v>-0.07950733733333333</v>
+        <v>-0.08148041741333333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.368734078941616</v>
+        <v>0.3753245703485878</v>
       </c>
       <c r="T52">
-        <v>1.586695321115792</v>
+        <v>1.619076858281421</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0271169936498472</v>
+        <v>0.02658528789200705</v>
       </c>
       <c r="W52">
-        <v>0.229405812897366</v>
+        <v>0.2295311891150647</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1129874735410299</v>
+        <v>0.1107720328833627</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.3009699459194911</v>
+        <v>0.302869945919491</v>
       </c>
       <c r="C53">
-        <v>0.1572270319730252</v>
+        <v>0.1410009404693975</v>
       </c>
       <c r="D53">
-        <v>0.7057370319730252</v>
+        <v>0.7005209404693975</v>
       </c>
       <c r="E53">
-        <v>0.5205099999999999</v>
+        <v>0.53152</v>
       </c>
       <c r="F53">
-        <v>0.56151</v>
+        <v>0.57252</v>
       </c>
       <c r="G53">
         <v>0.013</v>
@@ -5615,37 +5615,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M53">
-        <v>0.132404058</v>
+        <v>0.135000216</v>
       </c>
       <c r="N53">
-        <v>-0.1177373913333333</v>
+        <v>-0.1203335493333333</v>
       </c>
       <c r="O53">
-        <v>-0.02825697392</v>
+        <v>-0.02888005184</v>
       </c>
       <c r="P53">
-        <v>-0.08948041741333333</v>
+        <v>-0.09145349749333334</v>
       </c>
       <c r="Q53">
-        <v>-0.08148041741333333</v>
+        <v>-0.08345349749333333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3753245703485878</v>
+        <v>0.3821896655641834</v>
       </c>
       <c r="T53">
-        <v>1.619076858281421</v>
+        <v>1.652807626162283</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02658528789200705</v>
+        <v>0.0260740323556223</v>
       </c>
       <c r="W53">
-        <v>0.2295311891150647</v>
+        <v>0.2296517431705443</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1107720328833627</v>
+        <v>0.1086418014817595</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.302869945919491</v>
+        <v>0.304769945919491</v>
       </c>
       <c r="C54">
-        <v>0.1410009404693975</v>
+        <v>0.1248513873750564</v>
       </c>
       <c r="D54">
-        <v>0.7005209404693975</v>
+        <v>0.6953813873750564</v>
       </c>
       <c r="E54">
-        <v>0.53152</v>
+        <v>0.54253</v>
       </c>
       <c r="F54">
-        <v>0.57252</v>
+        <v>0.58353</v>
       </c>
       <c r="G54">
         <v>0.013</v>
@@ -5697,37 +5697,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M54">
-        <v>0.135000216</v>
+        <v>0.137596374</v>
       </c>
       <c r="N54">
-        <v>-0.1203335493333333</v>
+        <v>-0.1229297073333333</v>
       </c>
       <c r="O54">
-        <v>-0.02888005184</v>
+        <v>-0.02950312976</v>
       </c>
       <c r="P54">
-        <v>-0.09145349749333334</v>
+        <v>-0.09342657757333334</v>
       </c>
       <c r="Q54">
-        <v>-0.08345349749333333</v>
+        <v>-0.08542657757333333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3821896655641834</v>
+        <v>0.3893468924910809</v>
       </c>
       <c r="T54">
-        <v>1.652807626162283</v>
+        <v>1.687973745867864</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.0260740323556223</v>
+        <v>0.02558206948098792</v>
       </c>
       <c r="W54">
-        <v>0.2296517431705443</v>
+        <v>0.2297677480163831</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1086418014817595</v>
+        <v>0.106591956170783</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.304769945919491</v>
+        <v>0.306669945919491</v>
       </c>
       <c r="C55">
-        <v>0.1248513873750564</v>
+        <v>0.1087767003281996</v>
       </c>
       <c r="D55">
-        <v>0.6953813873750564</v>
+        <v>0.6903167003281997</v>
       </c>
       <c r="E55">
-        <v>0.54253</v>
+        <v>0.55354</v>
       </c>
       <c r="F55">
-        <v>0.58353</v>
+        <v>0.5945400000000001</v>
       </c>
       <c r="G55">
         <v>0.013</v>
@@ -5779,37 +5779,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M55">
-        <v>0.137596374</v>
+        <v>0.140192532</v>
       </c>
       <c r="N55">
-        <v>-0.1229297073333333</v>
+        <v>-0.1255258653333333</v>
       </c>
       <c r="O55">
-        <v>-0.02950312976</v>
+        <v>-0.03012620768</v>
       </c>
       <c r="P55">
-        <v>-0.09342657757333334</v>
+        <v>-0.09539965765333334</v>
       </c>
       <c r="Q55">
-        <v>-0.08542657757333333</v>
+        <v>-0.08739965765333334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3893468924910809</v>
+        <v>0.3968153031974088</v>
       </c>
       <c r="T55">
-        <v>1.687973745867864</v>
+        <v>1.724668827299774</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02558206948098792</v>
+        <v>0.02510832745356222</v>
       </c>
       <c r="W55">
-        <v>0.2297677480163831</v>
+        <v>0.22987945638645</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.106591956170783</v>
+        <v>0.1046180310565092</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.306669945919491</v>
+        <v>0.3085699459194911</v>
       </c>
       <c r="C56">
-        <v>0.1087767003281996</v>
+        <v>0.09277525533614028</v>
       </c>
       <c r="D56">
-        <v>0.6903167003281997</v>
+        <v>0.6853252553361403</v>
       </c>
       <c r="E56">
-        <v>0.55354</v>
+        <v>0.56455</v>
       </c>
       <c r="F56">
-        <v>0.5945400000000001</v>
+        <v>0.60555</v>
       </c>
       <c r="G56">
         <v>0.013</v>
@@ -5861,37 +5861,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M56">
-        <v>0.140192532</v>
+        <v>0.14278869</v>
       </c>
       <c r="N56">
-        <v>-0.1255258653333333</v>
+        <v>-0.1281220233333334</v>
       </c>
       <c r="O56">
-        <v>-0.03012620768</v>
+        <v>-0.03074928560000001</v>
       </c>
       <c r="P56">
-        <v>-0.09539965765333334</v>
+        <v>-0.09737273773333335</v>
       </c>
       <c r="Q56">
-        <v>-0.08739965765333334</v>
+        <v>-0.08937273773333335</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3968153031974088</v>
+        <v>0.4046156432684623</v>
       </c>
       <c r="T56">
-        <v>1.724668827299774</v>
+        <v>1.762994801239769</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02510832745356222</v>
+        <v>0.02465181240895199</v>
       </c>
       <c r="W56">
-        <v>0.22987945638645</v>
+        <v>0.2299871026339691</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1046180310565092</v>
+        <v>0.1027158850372999</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.3085699459194911</v>
+        <v>0.310469945919491</v>
       </c>
       <c r="C57">
-        <v>0.09277525533614028</v>
+        <v>0.07684547503915595</v>
       </c>
       <c r="D57">
-        <v>0.6853252553361403</v>
+        <v>0.6804054750391559</v>
       </c>
       <c r="E57">
-        <v>0.56455</v>
+        <v>0.57556</v>
       </c>
       <c r="F57">
-        <v>0.60555</v>
+        <v>0.61656</v>
       </c>
       <c r="G57">
         <v>0.013</v>
@@ -5943,37 +5943,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M57">
-        <v>0.14278869</v>
+        <v>0.145384848</v>
       </c>
       <c r="N57">
-        <v>-0.1281220233333334</v>
+        <v>-0.1307181813333333</v>
       </c>
       <c r="O57">
-        <v>-0.03074928560000001</v>
+        <v>-0.03137236352</v>
       </c>
       <c r="P57">
-        <v>-0.09737273773333335</v>
+        <v>-0.09934581781333335</v>
       </c>
       <c r="Q57">
-        <v>-0.08937273773333335</v>
+        <v>-0.09134581781333334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.4046156432684623</v>
+        <v>0.4127705442518363</v>
       </c>
       <c r="T57">
-        <v>1.762994801239769</v>
+        <v>1.803062864904309</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02465181240895199</v>
+        <v>0.02421160147307785</v>
       </c>
       <c r="W57">
-        <v>0.2299871026339691</v>
+        <v>0.2300909043726483</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1027158850372999</v>
+        <v>0.100881672804491</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.310469945919491</v>
+        <v>0.3123699459194911</v>
       </c>
       <c r="C58">
-        <v>0.07684547503915595</v>
+        <v>0.06098582704858735</v>
       </c>
       <c r="D58">
-        <v>0.6804054750391559</v>
+        <v>0.6755558270485874</v>
       </c>
       <c r="E58">
-        <v>0.57556</v>
+        <v>0.58657</v>
       </c>
       <c r="F58">
-        <v>0.61656</v>
+        <v>0.6275700000000001</v>
       </c>
       <c r="G58">
         <v>0.013</v>
@@ -6025,37 +6025,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M58">
-        <v>0.145384848</v>
+        <v>0.147981006</v>
       </c>
       <c r="N58">
-        <v>-0.1307181813333333</v>
+        <v>-0.1333143393333334</v>
       </c>
       <c r="O58">
-        <v>-0.03137236352</v>
+        <v>-0.03199544144000001</v>
       </c>
       <c r="P58">
-        <v>-0.09934581781333335</v>
+        <v>-0.1013188978933334</v>
       </c>
       <c r="Q58">
-        <v>-0.09134581781333334</v>
+        <v>-0.09331889789333335</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.4127705442518363</v>
+        <v>0.4213047429553676</v>
       </c>
       <c r="T58">
-        <v>1.803062864904309</v>
+        <v>1.844994559436968</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02421160147307785</v>
+        <v>0.02378683653495367</v>
       </c>
       <c r="W58">
-        <v>0.2300909043726483</v>
+        <v>0.2301910639450579</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.100881672804491</v>
+        <v>0.09911181889564025</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.3123699459194911</v>
+        <v>0.314269945919491</v>
       </c>
       <c r="C59">
-        <v>0.06098582704858735</v>
+        <v>0.04519482235550631</v>
       </c>
       <c r="D59">
-        <v>0.6755558270485874</v>
+        <v>0.6707748223555063</v>
       </c>
       <c r="E59">
-        <v>0.58657</v>
+        <v>0.59758</v>
       </c>
       <c r="F59">
-        <v>0.6275700000000001</v>
+        <v>0.63858</v>
       </c>
       <c r="G59">
         <v>0.013</v>
@@ -6107,37 +6107,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M59">
-        <v>0.147981006</v>
+        <v>0.150577164</v>
       </c>
       <c r="N59">
-        <v>-0.1333143393333334</v>
+        <v>-0.1359104973333334</v>
       </c>
       <c r="O59">
-        <v>-0.03199544144000001</v>
+        <v>-0.03261851936</v>
       </c>
       <c r="P59">
-        <v>-0.1013188978933334</v>
+        <v>-0.1032919779733334</v>
       </c>
       <c r="Q59">
-        <v>-0.09331889789333335</v>
+        <v>-0.09529197797333334</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4213047429553676</v>
+        <v>0.4302453320733525</v>
       </c>
       <c r="T59">
-        <v>1.844994559436968</v>
+        <v>1.888923001328324</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02378683653495367</v>
+        <v>0.02337671866366137</v>
       </c>
       <c r="W59">
-        <v>0.2301910639450579</v>
+        <v>0.2302877697391086</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.09911181889564025</v>
+        <v>0.09740299443192235</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.314269945919491</v>
+        <v>0.316169945919491</v>
       </c>
       <c r="C60">
-        <v>0.04519482235550643</v>
+        <v>0.02947101380647865</v>
       </c>
       <c r="D60">
-        <v>0.6707748223555063</v>
+        <v>0.6660610138064786</v>
       </c>
       <c r="E60">
-        <v>0.5975799999999999</v>
+        <v>0.60859</v>
       </c>
       <c r="F60">
-        <v>0.6385799999999999</v>
+        <v>0.64959</v>
       </c>
       <c r="G60">
         <v>0.013</v>
@@ -6189,37 +6189,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M60">
-        <v>0.150577164</v>
+        <v>0.153173322</v>
       </c>
       <c r="N60">
-        <v>-0.1359104973333333</v>
+        <v>-0.1385066553333333</v>
       </c>
       <c r="O60">
-        <v>-0.03261851935999999</v>
+        <v>-0.03324159728</v>
       </c>
       <c r="P60">
-        <v>-0.1032919779733333</v>
+        <v>-0.1052650580533333</v>
       </c>
       <c r="Q60">
-        <v>-0.09529197797333333</v>
+        <v>-0.09726505805333333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4302453320733524</v>
+        <v>0.4396220474897756</v>
       </c>
       <c r="T60">
-        <v>1.888923001328324</v>
+        <v>1.934994294043648</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02337671866366138</v>
+        <v>0.02298050309309084</v>
       </c>
       <c r="W60">
-        <v>0.2302877697391086</v>
+        <v>0.2303811973706492</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.09740299443192235</v>
+        <v>0.09575209622121184</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.316169945919491</v>
+        <v>0.318069945919491</v>
       </c>
       <c r="C61">
-        <v>0.02947101380647865</v>
+        <v>0.01381299464314978</v>
       </c>
       <c r="D61">
-        <v>0.6660610138064786</v>
+        <v>0.6614129946431497</v>
       </c>
       <c r="E61">
-        <v>0.60859</v>
+        <v>0.6195999999999999</v>
       </c>
       <c r="F61">
-        <v>0.64959</v>
+        <v>0.6606</v>
       </c>
       <c r="G61">
         <v>0.013</v>
@@ -6271,37 +6271,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M61">
-        <v>0.153173322</v>
+        <v>0.15576948</v>
       </c>
       <c r="N61">
-        <v>-0.1385066553333333</v>
+        <v>-0.1411028133333333</v>
       </c>
       <c r="O61">
-        <v>-0.03324159728</v>
+        <v>-0.0338646752</v>
       </c>
       <c r="P61">
-        <v>-0.1052650580533333</v>
+        <v>-0.1072381381333333</v>
       </c>
       <c r="Q61">
-        <v>-0.09726505805333333</v>
+        <v>-0.09923813813333332</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4396220474897756</v>
+        <v>0.44946759867702</v>
       </c>
       <c r="T61">
-        <v>1.934994294043648</v>
+        <v>1.98336915139474</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02298050309309084</v>
+        <v>0.022597494708206</v>
       </c>
       <c r="W61">
-        <v>0.2303811973706492</v>
+        <v>0.230471510747805</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.09575209622121184</v>
+        <v>0.09415622795085832</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.318069945919491</v>
+        <v>0.319969945919491</v>
       </c>
       <c r="C62">
-        <v>0.01381299464314978</v>
+        <v>-0.001780602897446415</v>
       </c>
       <c r="D62">
-        <v>0.6614129946431497</v>
+        <v>0.6568293971025535</v>
       </c>
       <c r="E62">
-        <v>0.6195999999999999</v>
+        <v>0.6306099999999999</v>
       </c>
       <c r="F62">
-        <v>0.6606</v>
+        <v>0.6716099999999999</v>
       </c>
       <c r="G62">
         <v>0.013</v>
@@ -6353,37 +6353,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M62">
-        <v>0.15576948</v>
+        <v>0.158365638</v>
       </c>
       <c r="N62">
-        <v>-0.1411028133333333</v>
+        <v>-0.1436989713333333</v>
       </c>
       <c r="O62">
-        <v>-0.0338646752</v>
+        <v>-0.03448775312</v>
       </c>
       <c r="P62">
-        <v>-0.1072381381333333</v>
+        <v>-0.1092112182133333</v>
       </c>
       <c r="Q62">
-        <v>-0.09923813813333332</v>
+        <v>-0.1012112182133333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.44946759867702</v>
+        <v>0.4598180499251487</v>
       </c>
       <c r="T62">
-        <v>1.98336915139474</v>
+        <v>2.034224770661272</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.022597494708206</v>
+        <v>0.02222704397528459</v>
       </c>
       <c r="W62">
-        <v>0.230471510747805</v>
+        <v>0.2305588630306279</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.09415622795085832</v>
+        <v>0.09261268323035243</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.319969945919491</v>
+        <v>0.321869945919491</v>
       </c>
       <c r="C63">
-        <v>-0.001780602897446415</v>
+        <v>-0.0173111089247806</v>
       </c>
       <c r="D63">
-        <v>0.6568293971025535</v>
+        <v>0.6523088910752194</v>
       </c>
       <c r="E63">
-        <v>0.6306099999999999</v>
+        <v>0.64162</v>
       </c>
       <c r="F63">
-        <v>0.6716099999999999</v>
+        <v>0.68262</v>
       </c>
       <c r="G63">
         <v>0.013</v>
@@ -6435,37 +6435,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M63">
-        <v>0.158365638</v>
+        <v>0.160961796</v>
       </c>
       <c r="N63">
-        <v>-0.1436989713333333</v>
+        <v>-0.1462951293333334</v>
       </c>
       <c r="O63">
-        <v>-0.03448775312</v>
+        <v>-0.03511083104000001</v>
       </c>
       <c r="P63">
-        <v>-0.1092112182133333</v>
+        <v>-0.1111842982933333</v>
       </c>
       <c r="Q63">
-        <v>-0.1012112182133333</v>
+        <v>-0.1031842982933333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4598180499251487</v>
+        <v>0.4707132617652842</v>
       </c>
       <c r="T63">
-        <v>2.034224770661272</v>
+        <v>2.087757001468147</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02222704397528459</v>
+        <v>0.0218685432660058</v>
       </c>
       <c r="W63">
-        <v>0.2305588630306279</v>
+        <v>0.2306433974978758</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.09261268323035243</v>
+        <v>0.09111893027502416</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.321869945919491</v>
+        <v>0.323769945919491</v>
       </c>
       <c r="C64">
-        <v>-0.0173111089247806</v>
+        <v>-0.03277981718168654</v>
       </c>
       <c r="D64">
-        <v>0.6523088910752194</v>
+        <v>0.6478501828183134</v>
       </c>
       <c r="E64">
-        <v>0.64162</v>
+        <v>0.6526299999999999</v>
       </c>
       <c r="F64">
-        <v>0.68262</v>
+        <v>0.69363</v>
       </c>
       <c r="G64">
         <v>0.013</v>
@@ -6517,37 +6517,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M64">
-        <v>0.160961796</v>
+        <v>0.163557954</v>
       </c>
       <c r="N64">
-        <v>-0.1462951293333334</v>
+        <v>-0.1488912873333333</v>
       </c>
       <c r="O64">
-        <v>-0.03511083104000001</v>
+        <v>-0.03573390896</v>
       </c>
       <c r="P64">
-        <v>-0.1111842982933333</v>
+        <v>-0.1131573783733333</v>
       </c>
       <c r="Q64">
-        <v>-0.1031842982933333</v>
+        <v>-0.1051573783733333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4707132617652842</v>
+        <v>0.4821974039751568</v>
       </c>
       <c r="T64">
-        <v>2.087757001468147</v>
+        <v>2.144182866372692</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0218685432660058</v>
+        <v>0.02152142353162476</v>
       </c>
       <c r="W64">
-        <v>0.2306433974978758</v>
+        <v>0.2307252483312429</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.09111893027502416</v>
+        <v>0.08967259804843641</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.323769945919491</v>
+        <v>0.3256699459194911</v>
       </c>
       <c r="C65">
-        <v>-0.03277981718168654</v>
+        <v>-0.04818798627880316</v>
       </c>
       <c r="D65">
-        <v>0.6478501828183134</v>
+        <v>0.6434520137211969</v>
       </c>
       <c r="E65">
-        <v>0.6526299999999999</v>
+        <v>0.66364</v>
       </c>
       <c r="F65">
-        <v>0.69363</v>
+        <v>0.70464</v>
       </c>
       <c r="G65">
         <v>0.013</v>
@@ -6599,37 +6599,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M65">
-        <v>0.163557954</v>
+        <v>0.166154112</v>
       </c>
       <c r="N65">
-        <v>-0.1488912873333333</v>
+        <v>-0.1514874453333334</v>
       </c>
       <c r="O65">
-        <v>-0.03573390896</v>
+        <v>-0.03635698688</v>
       </c>
       <c r="P65">
-        <v>-0.1131573783733333</v>
+        <v>-0.1151304584533334</v>
       </c>
       <c r="Q65">
-        <v>-0.1051573783733333</v>
+        <v>-0.1071304584533334</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4821974039751568</v>
+        <v>0.4943195540855778</v>
       </c>
       <c r="T65">
-        <v>2.144182866372692</v>
+        <v>2.203743501549711</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02152142353162476</v>
+        <v>0.02118515128894312</v>
       </c>
       <c r="W65">
-        <v>0.2307252483312429</v>
+        <v>0.2308045413260672</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.08967259804843641</v>
+        <v>0.08827146370392969</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.3256699459194911</v>
+        <v>0.327569945919491</v>
       </c>
       <c r="C66">
-        <v>-0.04818798627880316</v>
+        <v>-0.06353684087907174</v>
       </c>
       <c r="D66">
-        <v>0.6434520137211969</v>
+        <v>0.6391131591209283</v>
       </c>
       <c r="E66">
-        <v>0.66364</v>
+        <v>0.67465</v>
       </c>
       <c r="F66">
-        <v>0.70464</v>
+        <v>0.71565</v>
       </c>
       <c r="G66">
         <v>0.013</v>
@@ -6681,37 +6681,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M66">
-        <v>0.166154112</v>
+        <v>0.16875027</v>
       </c>
       <c r="N66">
-        <v>-0.1514874453333334</v>
+        <v>-0.1540836033333333</v>
       </c>
       <c r="O66">
-        <v>-0.03635698688</v>
+        <v>-0.0369800648</v>
       </c>
       <c r="P66">
-        <v>-0.1151304584533334</v>
+        <v>-0.1171035385333333</v>
       </c>
       <c r="Q66">
-        <v>-0.1071304584533334</v>
+        <v>-0.1091035385333333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4943195540855778</v>
+        <v>0.5071343984880229</v>
       </c>
       <c r="T66">
-        <v>2.203743501549711</v>
+        <v>2.266707601593989</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02118515128894312</v>
+        <v>0.02085922588449784</v>
       </c>
       <c r="W66">
-        <v>0.2308045413260672</v>
+        <v>0.2308813945364354</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.08827146370392969</v>
+        <v>0.08691344118540767</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.327569945919491</v>
+        <v>0.329469945919491</v>
       </c>
       <c r="C67">
-        <v>-0.06353684087907174</v>
+        <v>-0.07882757283463249</v>
       </c>
       <c r="D67">
-        <v>0.6391131591209283</v>
+        <v>0.6348324271653675</v>
       </c>
       <c r="E67">
-        <v>0.67465</v>
+        <v>0.6856599999999999</v>
       </c>
       <c r="F67">
-        <v>0.71565</v>
+        <v>0.72666</v>
       </c>
       <c r="G67">
         <v>0.013</v>
@@ -6763,37 +6763,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M67">
-        <v>0.16875027</v>
+        <v>0.171346428</v>
       </c>
       <c r="N67">
-        <v>-0.1540836033333333</v>
+        <v>-0.1566797613333333</v>
       </c>
       <c r="O67">
-        <v>-0.0369800648</v>
+        <v>-0.03760314272</v>
       </c>
       <c r="P67">
-        <v>-0.1171035385333333</v>
+        <v>-0.1190766186133333</v>
       </c>
       <c r="Q67">
-        <v>-0.1091035385333333</v>
+        <v>-0.1110766186133333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.5071343984880229</v>
+        <v>0.5207030572670823</v>
       </c>
       <c r="T67">
-        <v>2.266707601593989</v>
+        <v>2.333375472229106</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02085922588449784</v>
+        <v>0.02054317700746</v>
       </c>
       <c r="W67">
-        <v>0.2308813945364354</v>
+        <v>0.2309559188616409</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.08691344118540767</v>
+        <v>0.08559657086441663</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.329469945919491</v>
+        <v>0.331369945919491</v>
       </c>
       <c r="C68">
-        <v>-0.07882757283463249</v>
+        <v>-0.09406134227833407</v>
       </c>
       <c r="D68">
-        <v>0.6348324271653675</v>
+        <v>0.630608657721666</v>
       </c>
       <c r="E68">
-        <v>0.6856599999999999</v>
+        <v>0.69667</v>
       </c>
       <c r="F68">
-        <v>0.72666</v>
+        <v>0.73767</v>
       </c>
       <c r="G68">
         <v>0.013</v>
@@ -6845,37 +6845,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M68">
-        <v>0.171346428</v>
+        <v>0.173942586</v>
       </c>
       <c r="N68">
-        <v>-0.1566797613333333</v>
+        <v>-0.1592759193333333</v>
       </c>
       <c r="O68">
-        <v>-0.03760314272</v>
+        <v>-0.03822622064</v>
       </c>
       <c r="P68">
-        <v>-0.1190766186133333</v>
+        <v>-0.1210496986933333</v>
       </c>
       <c r="Q68">
-        <v>-0.1110766186133333</v>
+        <v>-0.1130496986933333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.5207030572670823</v>
+        <v>0.5350940590024486</v>
       </c>
       <c r="T68">
-        <v>2.333375472229106</v>
+        <v>2.404083819872413</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02054317700746</v>
+        <v>0.0202365624252591</v>
       </c>
       <c r="W68">
-        <v>0.2309559188616409</v>
+        <v>0.2310282185801239</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.08559657086441663</v>
+        <v>0.08431901010524623</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.331369945919491</v>
+        <v>0.333269945919491</v>
       </c>
       <c r="C69">
-        <v>-0.09406134227833407</v>
+        <v>-0.1092392786719586</v>
       </c>
       <c r="D69">
-        <v>0.630608657721666</v>
+        <v>0.6264407213280414</v>
       </c>
       <c r="E69">
-        <v>0.69667</v>
+        <v>0.70768</v>
       </c>
       <c r="F69">
-        <v>0.73767</v>
+        <v>0.74868</v>
       </c>
       <c r="G69">
         <v>0.013</v>
@@ -6927,37 +6927,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M69">
-        <v>0.173942586</v>
+        <v>0.176538744</v>
       </c>
       <c r="N69">
-        <v>-0.1592759193333333</v>
+        <v>-0.1618720773333333</v>
       </c>
       <c r="O69">
-        <v>-0.03822622064</v>
+        <v>-0.03884929856</v>
       </c>
       <c r="P69">
-        <v>-0.1210496986933333</v>
+        <v>-0.1230227787733333</v>
       </c>
       <c r="Q69">
-        <v>-0.1130496986933333</v>
+        <v>-0.1150227787733333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.5350940590024486</v>
+        <v>0.550384498346275</v>
       </c>
       <c r="T69">
-        <v>2.404083819872413</v>
+        <v>2.479211439243425</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0202365624252591</v>
+        <v>0.01993896591900529</v>
       </c>
       <c r="W69">
-        <v>0.2310282185801239</v>
+        <v>0.2310983918362986</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.08431901010524623</v>
+        <v>0.08307902466252204</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.333269945919491</v>
+        <v>0.335169945919491</v>
       </c>
       <c r="C70">
-        <v>-0.1092392786719586</v>
+        <v>-0.124362481813153</v>
       </c>
       <c r="D70">
-        <v>0.6264407213280414</v>
+        <v>0.6223275181868471</v>
       </c>
       <c r="E70">
-        <v>0.70768</v>
+        <v>0.7186900000000001</v>
       </c>
       <c r="F70">
-        <v>0.74868</v>
+        <v>0.7596900000000001</v>
       </c>
       <c r="G70">
         <v>0.013</v>
@@ -7009,37 +7009,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M70">
-        <v>0.176538744</v>
+        <v>0.179134902</v>
       </c>
       <c r="N70">
-        <v>-0.1618720773333333</v>
+        <v>-0.1644682353333334</v>
       </c>
       <c r="O70">
-        <v>-0.03884929856</v>
+        <v>-0.03947237648000001</v>
       </c>
       <c r="P70">
-        <v>-0.1230227787733333</v>
+        <v>-0.1249958588533334</v>
       </c>
       <c r="Q70">
-        <v>-0.1150227787733333</v>
+        <v>-0.1169958588533334</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.550384498346275</v>
+        <v>0.5666614176477678</v>
       </c>
       <c r="T70">
-        <v>2.479211439243425</v>
+        <v>2.559186001799665</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01993896591900529</v>
+        <v>0.01964999539843999</v>
       </c>
       <c r="W70">
-        <v>0.2310983918362986</v>
+        <v>0.2311665310850478</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.08307902466252204</v>
+        <v>0.08187498082683331</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.335169945919491</v>
+        <v>0.337069945919491</v>
       </c>
       <c r="C71">
-        <v>-0.124362481813153</v>
+        <v>-0.1394320228029461</v>
       </c>
       <c r="D71">
-        <v>0.6223275181868471</v>
+        <v>0.618267977197054</v>
       </c>
       <c r="E71">
-        <v>0.7186900000000001</v>
+        <v>0.7297</v>
       </c>
       <c r="F71">
-        <v>0.7596900000000001</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="G71">
         <v>0.013</v>
@@ -7091,37 +7091,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M71">
-        <v>0.179134902</v>
+        <v>0.18173106</v>
       </c>
       <c r="N71">
-        <v>-0.1644682353333334</v>
+        <v>-0.1670643933333334</v>
       </c>
       <c r="O71">
-        <v>-0.03947237648000001</v>
+        <v>-0.04009545440000001</v>
       </c>
       <c r="P71">
-        <v>-0.1249958588533334</v>
+        <v>-0.1269689389333334</v>
       </c>
       <c r="Q71">
-        <v>-0.1169958588533334</v>
+        <v>-0.1189689389333334</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.5666614176477678</v>
+        <v>0.5840234649026934</v>
       </c>
       <c r="T71">
-        <v>2.559186001799665</v>
+        <v>2.644492201859654</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01964999539843999</v>
+        <v>0.01936928117846228</v>
       </c>
       <c r="W71">
-        <v>0.2311665310850478</v>
+        <v>0.2312327234981186</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.08187498082683331</v>
+        <v>0.08070533824359283</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.337069945919491</v>
+        <v>0.3389699459194911</v>
       </c>
       <c r="C72">
-        <v>-0.1394320228029461</v>
+        <v>-0.1544489449756474</v>
       </c>
       <c r="D72">
-        <v>0.618267977197054</v>
+        <v>0.6142610550243526</v>
       </c>
       <c r="E72">
-        <v>0.7297</v>
+        <v>0.74071</v>
       </c>
       <c r="F72">
-        <v>0.7707000000000001</v>
+        <v>0.78171</v>
       </c>
       <c r="G72">
         <v>0.013</v>
@@ -7173,37 +7173,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M72">
-        <v>0.18173106</v>
+        <v>0.184327218</v>
       </c>
       <c r="N72">
-        <v>-0.1670643933333334</v>
+        <v>-0.1696605513333334</v>
       </c>
       <c r="O72">
-        <v>-0.04009545440000001</v>
+        <v>-0.04071853232</v>
       </c>
       <c r="P72">
-        <v>-0.1269689389333334</v>
+        <v>-0.1289420190133334</v>
       </c>
       <c r="Q72">
-        <v>-0.1189689389333334</v>
+        <v>-0.1209420190133333</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.5840234649026934</v>
+        <v>0.6025828947269244</v>
       </c>
       <c r="T72">
-        <v>2.644492201859654</v>
+        <v>2.735681588130677</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01936928117846228</v>
+        <v>0.01909647440130084</v>
       </c>
       <c r="W72">
-        <v>0.2312327234981186</v>
+        <v>0.2312970513361733</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.08070533824359283</v>
+        <v>0.07956864333875346</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.338969945919491</v>
+        <v>0.340869945919491</v>
       </c>
       <c r="C73">
-        <v>-0.1544489449756473</v>
+        <v>-0.1694142647928161</v>
       </c>
       <c r="D73">
-        <v>0.6142610550243526</v>
+        <v>0.6103057352071839</v>
       </c>
       <c r="E73">
-        <v>0.7407099999999999</v>
+        <v>0.7517199999999999</v>
       </c>
       <c r="F73">
-        <v>0.7817099999999999</v>
+        <v>0.79272</v>
       </c>
       <c r="G73">
         <v>0.013</v>
@@ -7255,37 +7255,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M73">
-        <v>0.184327218</v>
+        <v>0.186923376</v>
       </c>
       <c r="N73">
-        <v>-0.1696605513333333</v>
+        <v>-0.1722567093333333</v>
       </c>
       <c r="O73">
-        <v>-0.04071853231999999</v>
+        <v>-0.04134161024</v>
       </c>
       <c r="P73">
-        <v>-0.1289420190133333</v>
+        <v>-0.1309150990933333</v>
       </c>
       <c r="Q73">
-        <v>-0.1209420190133333</v>
+        <v>-0.1229150990933333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.6025828947269242</v>
+        <v>0.6224679981100286</v>
       </c>
       <c r="T73">
-        <v>2.735681588130676</v>
+        <v>2.833384501992486</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01909647440130085</v>
+        <v>0.01883124559017166</v>
       </c>
       <c r="W73">
-        <v>0.2312970513361733</v>
+        <v>0.2313595922898375</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.07956864333875346</v>
+        <v>0.07846352329238193</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.340869945919491</v>
+        <v>0.342769945919491</v>
       </c>
       <c r="C74">
-        <v>-0.1694142647928161</v>
+        <v>-0.1843289727029154</v>
       </c>
       <c r="D74">
-        <v>0.6103057352071839</v>
+        <v>0.6064010272970846</v>
       </c>
       <c r="E74">
-        <v>0.7517199999999999</v>
+        <v>0.7627299999999999</v>
       </c>
       <c r="F74">
-        <v>0.79272</v>
+        <v>0.8037299999999999</v>
       </c>
       <c r="G74">
         <v>0.013</v>
@@ -7337,37 +7337,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M74">
-        <v>0.186923376</v>
+        <v>0.189519534</v>
       </c>
       <c r="N74">
-        <v>-0.1722567093333333</v>
+        <v>-0.1748528673333333</v>
       </c>
       <c r="O74">
-        <v>-0.04134161024</v>
+        <v>-0.04196468816</v>
       </c>
       <c r="P74">
-        <v>-0.1309150990933333</v>
+        <v>-0.1328881791733333</v>
       </c>
       <c r="Q74">
-        <v>-0.1229150990933333</v>
+        <v>-0.1248881791733333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.6224679981100286</v>
+        <v>0.6438260721141037</v>
       </c>
       <c r="T74">
-        <v>2.833384501992486</v>
+        <v>2.938324668732948</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01883124559017166</v>
+        <v>0.01857328332181315</v>
       </c>
       <c r="W74">
-        <v>0.2313595922898375</v>
+        <v>0.2314204197927165</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.07846352329238193</v>
+        <v>0.07738868050755476</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.342769945919491</v>
+        <v>0.344669945919491</v>
       </c>
       <c r="C75">
-        <v>-0.1843289727029154</v>
+        <v>-0.199194033968175</v>
       </c>
       <c r="D75">
-        <v>0.6064010272970846</v>
+        <v>0.602545966031825</v>
       </c>
       <c r="E75">
-        <v>0.7627299999999999</v>
+        <v>0.77374</v>
       </c>
       <c r="F75">
-        <v>0.8037299999999999</v>
+        <v>0.81474</v>
       </c>
       <c r="G75">
         <v>0.013</v>
@@ -7419,37 +7419,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M75">
-        <v>0.189519534</v>
+        <v>0.192115692</v>
       </c>
       <c r="N75">
-        <v>-0.1748528673333333</v>
+        <v>-0.1774490253333333</v>
       </c>
       <c r="O75">
-        <v>-0.04196468816</v>
+        <v>-0.04258776608</v>
       </c>
       <c r="P75">
-        <v>-0.1328881791733333</v>
+        <v>-0.1348612592533333</v>
       </c>
       <c r="Q75">
-        <v>-0.1248881791733333</v>
+        <v>-0.1268612592533333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.6438260721141037</v>
+        <v>0.666827074887723</v>
       </c>
       <c r="T75">
-        <v>2.938324668732948</v>
+        <v>3.051337155991908</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01857328332181315</v>
+        <v>0.01832229300665351</v>
       </c>
       <c r="W75">
-        <v>0.2314204197927165</v>
+        <v>0.2314796033090311</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.07738868050755476</v>
+        <v>0.07634288752772289</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.344669945919491</v>
+        <v>0.346569945919491</v>
       </c>
       <c r="C76">
-        <v>-0.199194033968175</v>
+        <v>-0.2140103894601129</v>
       </c>
       <c r="D76">
-        <v>0.602545966031825</v>
+        <v>0.5987396105398871</v>
       </c>
       <c r="E76">
-        <v>0.77374</v>
+        <v>0.7847499999999999</v>
       </c>
       <c r="F76">
-        <v>0.81474</v>
+        <v>0.82575</v>
       </c>
       <c r="G76">
         <v>0.013</v>
@@ -7501,37 +7501,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M76">
-        <v>0.192115692</v>
+        <v>0.19471185</v>
       </c>
       <c r="N76">
-        <v>-0.1774490253333333</v>
+        <v>-0.1800451833333333</v>
       </c>
       <c r="O76">
-        <v>-0.04258776608</v>
+        <v>-0.043210844</v>
       </c>
       <c r="P76">
-        <v>-0.1348612592533333</v>
+        <v>-0.1368343393333333</v>
       </c>
       <c r="Q76">
-        <v>-0.1268612592533333</v>
+        <v>-0.1288343393333333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.666827074887723</v>
+        <v>0.691668157883232</v>
       </c>
       <c r="T76">
-        <v>3.051337155991908</v>
+        <v>3.173390642231584</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01832229300665351</v>
+        <v>0.0180779957665648</v>
       </c>
       <c r="W76">
-        <v>0.2314796033090311</v>
+        <v>0.231537208598244</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.07634288752772289</v>
+        <v>0.07532498236068663</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.346569945919491</v>
+        <v>0.348469945919491</v>
       </c>
       <c r="C77">
-        <v>-0.2140103894601129</v>
+        <v>-0.2287789564250945</v>
       </c>
       <c r="D77">
-        <v>0.5987396105398871</v>
+        <v>0.5949810435749054</v>
       </c>
       <c r="E77">
-        <v>0.7847499999999999</v>
+        <v>0.7957599999999999</v>
       </c>
       <c r="F77">
-        <v>0.82575</v>
+        <v>0.8367599999999999</v>
       </c>
       <c r="G77">
         <v>0.013</v>
@@ -7583,37 +7583,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M77">
-        <v>0.19471185</v>
+        <v>0.197308008</v>
       </c>
       <c r="N77">
-        <v>-0.1800451833333333</v>
+        <v>-0.1826413413333333</v>
       </c>
       <c r="O77">
-        <v>-0.043210844</v>
+        <v>-0.04383392192</v>
       </c>
       <c r="P77">
-        <v>-0.1368343393333333</v>
+        <v>-0.1388074194133334</v>
       </c>
       <c r="Q77">
-        <v>-0.1288343393333333</v>
+        <v>-0.1308074194133333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.691668157883232</v>
+        <v>0.7185793311283667</v>
       </c>
       <c r="T77">
-        <v>3.173390642231584</v>
+        <v>3.305615252324567</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0180779957665648</v>
+        <v>0.01784012740121526</v>
       </c>
       <c r="W77">
-        <v>0.231537208598244</v>
+        <v>0.2315932979587935</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.07532498236068663</v>
+        <v>0.07433386417173027</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.348469945919491</v>
+        <v>0.350369945919491</v>
       </c>
       <c r="C78">
-        <v>-0.2287789564250945</v>
+        <v>-0.2435006292212381</v>
       </c>
       <c r="D78">
-        <v>0.5949810435749054</v>
+        <v>0.591269370778762</v>
       </c>
       <c r="E78">
-        <v>0.7957599999999999</v>
+        <v>0.80677</v>
       </c>
       <c r="F78">
-        <v>0.8367599999999999</v>
+        <v>0.84777</v>
       </c>
       <c r="G78">
         <v>0.013</v>
@@ -7665,37 +7665,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M78">
-        <v>0.197308008</v>
+        <v>0.199904166</v>
       </c>
       <c r="N78">
-        <v>-0.1826413413333333</v>
+        <v>-0.1852374993333334</v>
       </c>
       <c r="O78">
-        <v>-0.04383392192</v>
+        <v>-0.04445699984</v>
       </c>
       <c r="P78">
-        <v>-0.1388074194133334</v>
+        <v>-0.1407804994933333</v>
       </c>
       <c r="Q78">
-        <v>-0.1308074194133333</v>
+        <v>-0.1327804994933333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.7185793311283667</v>
+        <v>0.7478306063948175</v>
       </c>
       <c r="T78">
-        <v>3.305615252324567</v>
+        <v>3.449337654599548</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01784012740121526</v>
+        <v>0.01760843743496571</v>
       </c>
       <c r="W78">
-        <v>0.2315932979587935</v>
+        <v>0.2316479304528351</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.07433386417173027</v>
+        <v>0.07336848931235707</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.350369945919491</v>
+        <v>0.352269945919491</v>
       </c>
       <c r="C79">
-        <v>-0.2435006292212381</v>
+        <v>-0.2581762800279073</v>
       </c>
       <c r="D79">
-        <v>0.591269370778762</v>
+        <v>0.5876037199720927</v>
       </c>
       <c r="E79">
-        <v>0.80677</v>
+        <v>0.81778</v>
       </c>
       <c r="F79">
-        <v>0.84777</v>
+        <v>0.85878</v>
       </c>
       <c r="G79">
         <v>0.013</v>
@@ -7747,37 +7747,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M79">
-        <v>0.199904166</v>
+        <v>0.202500324</v>
       </c>
       <c r="N79">
-        <v>-0.1852374993333334</v>
+        <v>-0.1878336573333333</v>
       </c>
       <c r="O79">
-        <v>-0.04445699984</v>
+        <v>-0.04508007776</v>
       </c>
       <c r="P79">
-        <v>-0.1407804994933333</v>
+        <v>-0.1427535795733333</v>
       </c>
       <c r="Q79">
-        <v>-0.1327804994933333</v>
+        <v>-0.1347535795733333</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.7478306063948175</v>
+        <v>0.7797410885036726</v>
       </c>
       <c r="T79">
-        <v>3.449337654599548</v>
+        <v>3.606125729808618</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01760843743496571</v>
+        <v>0.01738268823708154</v>
       </c>
       <c r="W79">
-        <v>0.2316479304528351</v>
+        <v>0.2317011621136962</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.07336848931235707</v>
+        <v>0.07242786765450637</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.352269945919491</v>
+        <v>0.354169945919491</v>
       </c>
       <c r="C80">
-        <v>-0.2581762800279073</v>
+        <v>-0.2728067595289755</v>
       </c>
       <c r="D80">
-        <v>0.5876037199720927</v>
+        <v>0.5839832404710246</v>
       </c>
       <c r="E80">
-        <v>0.81778</v>
+        <v>0.82879</v>
       </c>
       <c r="F80">
-        <v>0.85878</v>
+        <v>0.8697900000000001</v>
       </c>
       <c r="G80">
         <v>0.013</v>
@@ -7829,37 +7829,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M80">
-        <v>0.202500324</v>
+        <v>0.205096482</v>
       </c>
       <c r="N80">
-        <v>-0.1878336573333333</v>
+        <v>-0.1904298153333334</v>
       </c>
       <c r="O80">
-        <v>-0.04508007776</v>
+        <v>-0.04570315568</v>
       </c>
       <c r="P80">
-        <v>-0.1427535795733333</v>
+        <v>-0.1447266596533334</v>
       </c>
       <c r="Q80">
-        <v>-0.1347535795733333</v>
+        <v>-0.1367266596533334</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.7797410885036726</v>
+        <v>0.8146906641467049</v>
       </c>
       <c r="T80">
-        <v>3.606125729808618</v>
+        <v>3.777846002656648</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01738268823708154</v>
+        <v>0.01716265420876405</v>
       </c>
       <c r="W80">
-        <v>0.2317011621136962</v>
+        <v>0.2317530461375734</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.07242786765450637</v>
+        <v>0.07151105920318346</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.354169945919491</v>
+        <v>0.356069945919491</v>
       </c>
       <c r="C81">
-        <v>-0.2728067595289755</v>
+        <v>-0.287392897570985</v>
       </c>
       <c r="D81">
-        <v>0.5839832404710246</v>
+        <v>0.5804071024290151</v>
       </c>
       <c r="E81">
-        <v>0.82879</v>
+        <v>0.8398</v>
       </c>
       <c r="F81">
-        <v>0.8697900000000001</v>
+        <v>0.8808</v>
       </c>
       <c r="G81">
         <v>0.013</v>
@@ -7911,37 +7911,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M81">
-        <v>0.205096482</v>
+        <v>0.20769264</v>
       </c>
       <c r="N81">
-        <v>-0.1904298153333334</v>
+        <v>-0.1930259733333334</v>
       </c>
       <c r="O81">
-        <v>-0.04570315568</v>
+        <v>-0.0463262336</v>
       </c>
       <c r="P81">
-        <v>-0.1447266596533334</v>
+        <v>-0.1466997397333333</v>
       </c>
       <c r="Q81">
-        <v>-0.1367266596533334</v>
+        <v>-0.1386997397333333</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.8146906641467049</v>
+        <v>0.8531351973540402</v>
       </c>
       <c r="T81">
-        <v>3.777846002656648</v>
+        <v>3.966738302789481</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01716265420876405</v>
+        <v>0.0169481210311545</v>
       </c>
       <c r="W81">
-        <v>0.2317530461375734</v>
+        <v>0.2318036330608538</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.07151105920318346</v>
+        <v>0.07061717096314368</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.356069945919491</v>
+        <v>0.3579699459194911</v>
       </c>
       <c r="C82">
-        <v>-0.287392897570985</v>
+        <v>-0.3019355037972727</v>
       </c>
       <c r="D82">
-        <v>0.5804071024290151</v>
+        <v>0.5768744962027272</v>
       </c>
       <c r="E82">
-        <v>0.8398</v>
+        <v>0.85081</v>
       </c>
       <c r="F82">
-        <v>0.8808</v>
+        <v>0.89181</v>
       </c>
       <c r="G82">
         <v>0.013</v>
@@ -7993,37 +7993,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M82">
-        <v>0.20769264</v>
+        <v>0.210288798</v>
       </c>
       <c r="N82">
-        <v>-0.1930259733333334</v>
+        <v>-0.1956221313333333</v>
       </c>
       <c r="O82">
-        <v>-0.0463262336</v>
+        <v>-0.04694931152</v>
       </c>
       <c r="P82">
-        <v>-0.1466997397333333</v>
+        <v>-0.1486728198133333</v>
       </c>
       <c r="Q82">
-        <v>-0.1386997397333333</v>
+        <v>-0.1406728198133333</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.8531351973540402</v>
+        <v>0.8956265235305687</v>
       </c>
       <c r="T82">
-        <v>3.966738302789481</v>
+        <v>4.175514002936296</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0169481210311545</v>
+        <v>0.01673888496904148</v>
       </c>
       <c r="W82">
-        <v>0.2318036330608538</v>
+        <v>0.2318529709243</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.07061717096314368</v>
+        <v>0.06974535403767279</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3579699459194911</v>
+        <v>0.3598699459194911</v>
       </c>
       <c r="C83">
-        <v>-0.3019355037972727</v>
+        <v>-0.3164353682590769</v>
       </c>
       <c r="D83">
-        <v>0.5768744962027272</v>
+        <v>0.5733846317409231</v>
       </c>
       <c r="E83">
-        <v>0.85081</v>
+        <v>0.86182</v>
       </c>
       <c r="F83">
-        <v>0.89181</v>
+        <v>0.9028200000000001</v>
       </c>
       <c r="G83">
         <v>0.013</v>
@@ -8075,37 +8075,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M83">
-        <v>0.210288798</v>
+        <v>0.212884956</v>
       </c>
       <c r="N83">
-        <v>-0.1956221313333333</v>
+        <v>-0.1982182893333334</v>
       </c>
       <c r="O83">
-        <v>-0.04694931152</v>
+        <v>-0.04757238944</v>
       </c>
       <c r="P83">
-        <v>-0.1486728198133333</v>
+        <v>-0.1506458998933334</v>
       </c>
       <c r="Q83">
-        <v>-0.1406728198133333</v>
+        <v>-0.1426458998933333</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.8956265235305687</v>
+        <v>0.942839108171156</v>
       </c>
       <c r="T83">
-        <v>4.175514002936296</v>
+        <v>4.407487003099424</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01673888496904148</v>
+        <v>0.01653475222551658</v>
       </c>
       <c r="W83">
-        <v>0.2318529709243</v>
+        <v>0.2319011054252232</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.06974535403767279</v>
+        <v>0.06889480093965239</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3598699459194911</v>
+        <v>0.361769945919491</v>
       </c>
       <c r="C84">
-        <v>-0.3164353682590769</v>
+        <v>-0.3308932620045958</v>
       </c>
       <c r="D84">
-        <v>0.5733846317409231</v>
+        <v>0.5699367379954042</v>
       </c>
       <c r="E84">
-        <v>0.86182</v>
+        <v>0.87283</v>
       </c>
       <c r="F84">
-        <v>0.9028200000000001</v>
+        <v>0.91383</v>
       </c>
       <c r="G84">
         <v>0.013</v>
@@ -8157,37 +8157,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M84">
-        <v>0.212884956</v>
+        <v>0.215481114</v>
       </c>
       <c r="N84">
-        <v>-0.1982182893333334</v>
+        <v>-0.2008144473333334</v>
       </c>
       <c r="O84">
-        <v>-0.04757238944</v>
+        <v>-0.04819546736000001</v>
       </c>
       <c r="P84">
-        <v>-0.1506458998933334</v>
+        <v>-0.1526189799733333</v>
       </c>
       <c r="Q84">
-        <v>-0.1426458998933333</v>
+        <v>-0.1446189799733333</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.942839108171156</v>
+        <v>0.995606114534165</v>
       </c>
       <c r="T84">
-        <v>4.407487003099424</v>
+        <v>4.666750944458213</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01653475222551658</v>
+        <v>0.01633553834328144</v>
       </c>
       <c r="W84">
-        <v>0.2319011054252232</v>
+        <v>0.2319480800586542</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.06889480093965239</v>
+        <v>0.06806474309700594</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.361769945919491</v>
+        <v>0.3636699459194911</v>
       </c>
       <c r="C85">
-        <v>-0.3308932620045958</v>
+        <v>-0.3453099376469216</v>
       </c>
       <c r="D85">
-        <v>0.5699367379954042</v>
+        <v>0.5665300623530785</v>
       </c>
       <c r="E85">
-        <v>0.87283</v>
+        <v>0.8838400000000001</v>
       </c>
       <c r="F85">
-        <v>0.91383</v>
+        <v>0.9248400000000001</v>
       </c>
       <c r="G85">
         <v>0.013</v>
@@ -8239,37 +8239,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M85">
-        <v>0.215481114</v>
+        <v>0.218077272</v>
       </c>
       <c r="N85">
-        <v>-0.2008144473333334</v>
+        <v>-0.2034106053333334</v>
       </c>
       <c r="O85">
-        <v>-0.04819546736000001</v>
+        <v>-0.04881854528000001</v>
       </c>
       <c r="P85">
-        <v>-0.1526189799733333</v>
+        <v>-0.1545920600533334</v>
       </c>
       <c r="Q85">
-        <v>-0.1446189799733333</v>
+        <v>-0.1465920600533334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.995606114534165</v>
+        <v>1.054968996692551</v>
       </c>
       <c r="T85">
-        <v>4.666750944458213</v>
+        <v>4.958422878486853</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01633553834328144</v>
+        <v>0.01614106764871857</v>
       </c>
       <c r="W85">
-        <v>0.2319480800586542</v>
+        <v>0.2319939362484322</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.06806474309700594</v>
+        <v>0.06725444853632734</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3636699459194911</v>
+        <v>0.3655699459194911</v>
       </c>
       <c r="C86">
-        <v>-0.3453099376469215</v>
+        <v>-0.359686129911725</v>
       </c>
       <c r="D86">
-        <v>0.5665300623530785</v>
+        <v>0.563163870088275</v>
       </c>
       <c r="E86">
-        <v>0.88384</v>
+        <v>0.8948499999999999</v>
       </c>
       <c r="F86">
-        <v>0.92484</v>
+        <v>0.93585</v>
       </c>
       <c r="G86">
         <v>0.013</v>
@@ -8321,37 +8321,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M86">
-        <v>0.218077272</v>
+        <v>0.22067343</v>
       </c>
       <c r="N86">
-        <v>-0.2034106053333334</v>
+        <v>-0.2060067633333333</v>
       </c>
       <c r="O86">
-        <v>-0.04881854528</v>
+        <v>-0.0494416232</v>
       </c>
       <c r="P86">
-        <v>-0.1545920600533334</v>
+        <v>-0.1565651401333333</v>
       </c>
       <c r="Q86">
-        <v>-0.1465920600533334</v>
+        <v>-0.1485651401333333</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.05496899669255</v>
+        <v>1.122246929805387</v>
       </c>
       <c r="T86">
-        <v>4.958422878486849</v>
+        <v>5.288984403719307</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01614106764871857</v>
+        <v>0.01595117273520423</v>
       </c>
       <c r="W86">
-        <v>0.2319939362484322</v>
+        <v>0.2320387134690389</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.06725444853632734</v>
+        <v>0.06646321973001756</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3655699459194911</v>
+        <v>0.3674699459194911</v>
       </c>
       <c r="C87">
-        <v>-0.359686129911725</v>
+        <v>-0.3740225561655333</v>
       </c>
       <c r="D87">
-        <v>0.563163870088275</v>
+        <v>0.5598374438344667</v>
       </c>
       <c r="E87">
-        <v>0.8948499999999999</v>
+        <v>0.9058599999999999</v>
       </c>
       <c r="F87">
-        <v>0.93585</v>
+        <v>0.9468599999999999</v>
       </c>
       <c r="G87">
         <v>0.013</v>
@@ -8403,37 +8403,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M87">
-        <v>0.22067343</v>
+        <v>0.223269588</v>
       </c>
       <c r="N87">
-        <v>-0.2060067633333333</v>
+        <v>-0.2086029213333333</v>
       </c>
       <c r="O87">
-        <v>-0.0494416232</v>
+        <v>-0.05006470112</v>
       </c>
       <c r="P87">
-        <v>-0.1565651401333333</v>
+        <v>-0.1585382202133333</v>
       </c>
       <c r="Q87">
-        <v>-0.1485651401333333</v>
+        <v>-0.1505382202133333</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.122246929805387</v>
+        <v>1.199135996220057</v>
       </c>
       <c r="T87">
-        <v>5.288984403719307</v>
+        <v>5.666769003984972</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01595117273520423</v>
+        <v>0.0157656939824693</v>
       </c>
       <c r="W87">
-        <v>0.2320387134690389</v>
+        <v>0.2320824493589337</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.06646321973001756</v>
+        <v>0.06569039159362211</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3674699459194911</v>
+        <v>0.369369945919491</v>
       </c>
       <c r="C88">
-        <v>-0.3740225561655333</v>
+        <v>-0.3883199169253925</v>
       </c>
       <c r="D88">
-        <v>0.5598374438344667</v>
+        <v>0.5565500830746075</v>
       </c>
       <c r="E88">
-        <v>0.9058599999999999</v>
+        <v>0.91687</v>
       </c>
       <c r="F88">
-        <v>0.9468599999999999</v>
+        <v>0.95787</v>
       </c>
       <c r="G88">
         <v>0.013</v>
@@ -8485,37 +8485,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M88">
-        <v>0.223269588</v>
+        <v>0.225865746</v>
       </c>
       <c r="N88">
-        <v>-0.2086029213333333</v>
+        <v>-0.2111990793333333</v>
       </c>
       <c r="O88">
-        <v>-0.05006470112</v>
+        <v>-0.05068777904</v>
       </c>
       <c r="P88">
-        <v>-0.1585382202133333</v>
+        <v>-0.1605113002933334</v>
       </c>
       <c r="Q88">
-        <v>-0.1505382202133333</v>
+        <v>-0.1525113002933333</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.199135996220057</v>
+        <v>1.287854149775446</v>
       </c>
       <c r="T88">
-        <v>5.666769003984972</v>
+        <v>6.102674311983815</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0157656939824693</v>
+        <v>0.01558447910910758</v>
       </c>
       <c r="W88">
-        <v>0.2320824493589337</v>
+        <v>0.2321251798260724</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.06569039159362211</v>
+        <v>0.06493532962128157</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.369369945919491</v>
+        <v>0.371269945919491</v>
       </c>
       <c r="C89">
-        <v>-0.3883199169253925</v>
+        <v>-0.4025788963506796</v>
       </c>
       <c r="D89">
-        <v>0.5565500830746075</v>
+        <v>0.5533011036493204</v>
       </c>
       <c r="E89">
-        <v>0.91687</v>
+        <v>0.9278799999999999</v>
       </c>
       <c r="F89">
-        <v>0.95787</v>
+        <v>0.96888</v>
       </c>
       <c r="G89">
         <v>0.013</v>
@@ -8567,37 +8567,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M89">
-        <v>0.225865746</v>
+        <v>0.228461904</v>
       </c>
       <c r="N89">
-        <v>-0.2111990793333333</v>
+        <v>-0.2137952373333333</v>
       </c>
       <c r="O89">
-        <v>-0.05068777904</v>
+        <v>-0.05131085696</v>
       </c>
       <c r="P89">
-        <v>-0.1605113002933334</v>
+        <v>-0.1624843803733333</v>
       </c>
       <c r="Q89">
-        <v>-0.1525113002933333</v>
+        <v>-0.1544843803733333</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.287854149775446</v>
+        <v>1.391358662256734</v>
       </c>
       <c r="T89">
-        <v>6.102674311983815</v>
+        <v>6.611230504649134</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01558447910910758</v>
+        <v>0.015407382755595</v>
       </c>
       <c r="W89">
-        <v>0.2321251798260724</v>
+        <v>0.2321669391462307</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.06493532962128157</v>
+        <v>0.06419742814831242</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.371269945919491</v>
+        <v>0.373169945919491</v>
       </c>
       <c r="C90">
-        <v>-0.4025788963506796</v>
+        <v>-0.4168001627177893</v>
       </c>
       <c r="D90">
-        <v>0.5533011036493204</v>
+        <v>0.5500898372822107</v>
       </c>
       <c r="E90">
-        <v>0.9278799999999999</v>
+        <v>0.93889</v>
       </c>
       <c r="F90">
-        <v>0.96888</v>
+        <v>0.97989</v>
       </c>
       <c r="G90">
         <v>0.013</v>
@@ -8649,37 +8649,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M90">
-        <v>0.228461904</v>
+        <v>0.231058062</v>
       </c>
       <c r="N90">
-        <v>-0.2137952373333333</v>
+        <v>-0.2163913953333333</v>
       </c>
       <c r="O90">
-        <v>-0.05131085696</v>
+        <v>-0.05193393488</v>
       </c>
       <c r="P90">
-        <v>-0.1624843803733333</v>
+        <v>-0.1644574604533333</v>
       </c>
       <c r="Q90">
-        <v>-0.1544843803733333</v>
+        <v>-0.1564574604533333</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.391358662256734</v>
+        <v>1.513682177007345</v>
       </c>
       <c r="T90">
-        <v>6.611230504649134</v>
+        <v>7.212251459617236</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.015407382755595</v>
+        <v>0.01523426609541977</v>
       </c>
       <c r="W90">
-        <v>0.2321669391462307</v>
+        <v>0.2322077600547</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.06419742814831242</v>
+        <v>0.06347610873091569</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.373169945919491</v>
+        <v>0.3750699459194911</v>
       </c>
       <c r="C91">
-        <v>-0.4168001627177893</v>
+        <v>-0.4309843688783834</v>
       </c>
       <c r="D91">
-        <v>0.5500898372822107</v>
+        <v>0.5469156311216166</v>
       </c>
       <c r="E91">
-        <v>0.93889</v>
+        <v>0.9499</v>
       </c>
       <c r="F91">
-        <v>0.97989</v>
+        <v>0.9909</v>
       </c>
       <c r="G91">
         <v>0.013</v>
@@ -8731,37 +8731,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M91">
-        <v>0.231058062</v>
+        <v>0.23365422</v>
       </c>
       <c r="N91">
-        <v>-0.2163913953333333</v>
+        <v>-0.2189875533333334</v>
       </c>
       <c r="O91">
-        <v>-0.05193393488</v>
+        <v>-0.0525570128</v>
       </c>
       <c r="P91">
-        <v>-0.1644574604533333</v>
+        <v>-0.1664305405333334</v>
       </c>
       <c r="Q91">
-        <v>-0.1564574604533333</v>
+        <v>-0.1584305405333334</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.513682177007345</v>
+        <v>1.660470394708081</v>
       </c>
       <c r="T91">
-        <v>7.212251459617236</v>
+        <v>7.933476605578963</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01523426609541977</v>
+        <v>0.01506499647213733</v>
       </c>
       <c r="W91">
-        <v>0.2322077600547</v>
+        <v>0.23224767383187</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.06347610873091569</v>
+        <v>0.06277081863390555</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3750699459194911</v>
+        <v>0.376969945919491</v>
       </c>
       <c r="C92">
-        <v>-0.4309843688783834</v>
+        <v>-0.44513215270187</v>
       </c>
       <c r="D92">
-        <v>0.5469156311216166</v>
+        <v>0.5437778472981301</v>
       </c>
       <c r="E92">
-        <v>0.9499</v>
+        <v>0.96091</v>
       </c>
       <c r="F92">
-        <v>0.9909</v>
+        <v>1.00191</v>
       </c>
       <c r="G92">
         <v>0.013</v>
@@ -8813,37 +8813,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M92">
-        <v>0.23365422</v>
+        <v>0.236250378</v>
       </c>
       <c r="N92">
-        <v>-0.2189875533333334</v>
+        <v>-0.2215837113333334</v>
       </c>
       <c r="O92">
-        <v>-0.0525570128</v>
+        <v>-0.05318009072000001</v>
       </c>
       <c r="P92">
-        <v>-0.1664305405333334</v>
+        <v>-0.1684036206133334</v>
       </c>
       <c r="Q92">
-        <v>-0.1584305405333334</v>
+        <v>-0.1604036206133334</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.660470394708081</v>
+        <v>1.839878216342312</v>
       </c>
       <c r="T92">
-        <v>7.933476605578963</v>
+        <v>8.814974006198847</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01506499647213733</v>
+        <v>0.0148994470603556</v>
       </c>
       <c r="W92">
-        <v>0.23224767383187</v>
+        <v>0.2322867103831681</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.06277081863390555</v>
+        <v>0.0620810294181483</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.376969945919491</v>
+        <v>0.378869945919491</v>
       </c>
       <c r="C93">
-        <v>-0.44513215270187</v>
+        <v>-0.4592441375027326</v>
       </c>
       <c r="D93">
-        <v>0.5437778472981301</v>
+        <v>0.5406758624972674</v>
       </c>
       <c r="E93">
-        <v>0.96091</v>
+        <v>0.97192</v>
       </c>
       <c r="F93">
-        <v>1.00191</v>
+        <v>1.01292</v>
       </c>
       <c r="G93">
         <v>0.013</v>
@@ -8895,37 +8895,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M93">
-        <v>0.236250378</v>
+        <v>0.238846536</v>
       </c>
       <c r="N93">
-        <v>-0.2215837113333334</v>
+        <v>-0.2241798693333334</v>
       </c>
       <c r="O93">
-        <v>-0.05318009072000001</v>
+        <v>-0.05380316864</v>
       </c>
       <c r="P93">
-        <v>-0.1684036206133334</v>
+        <v>-0.1703767006933334</v>
       </c>
       <c r="Q93">
-        <v>-0.1604036206133334</v>
+        <v>-0.1623767006933333</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.839878216342312</v>
+        <v>2.064137993385101</v>
       </c>
       <c r="T93">
-        <v>8.814974006198847</v>
+        <v>9.916845756973705</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0148994470603556</v>
+        <v>0.01473749654882999</v>
       </c>
       <c r="W93">
-        <v>0.2322867103831681</v>
+        <v>0.2323248983137859</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.0620810294181483</v>
+        <v>0.06140623562012493</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.378869945919491</v>
+        <v>0.3807699459194911</v>
       </c>
       <c r="C94">
-        <v>-0.4592441375027326</v>
+        <v>-0.4733209324533213</v>
       </c>
       <c r="D94">
-        <v>0.5406758624972674</v>
+        <v>0.5376090675466787</v>
       </c>
       <c r="E94">
-        <v>0.97192</v>
+        <v>0.98293</v>
       </c>
       <c r="F94">
-        <v>1.01292</v>
+        <v>1.02393</v>
       </c>
       <c r="G94">
         <v>0.013</v>
@@ -8977,37 +8977,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M94">
-        <v>0.238846536</v>
+        <v>0.241442694</v>
       </c>
       <c r="N94">
-        <v>-0.2241798693333334</v>
+        <v>-0.2267760273333334</v>
       </c>
       <c r="O94">
-        <v>-0.05380316864</v>
+        <v>-0.05442624656</v>
       </c>
       <c r="P94">
-        <v>-0.1703767006933334</v>
+        <v>-0.1723497807733333</v>
       </c>
       <c r="Q94">
-        <v>-0.1623767006933333</v>
+        <v>-0.1643497807733333</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>2.064137993385101</v>
+        <v>2.352471992440116</v>
       </c>
       <c r="T94">
-        <v>9.916845756973705</v>
+        <v>11.33353800796995</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01473749654882999</v>
+        <v>0.01457902884400387</v>
       </c>
       <c r="W94">
-        <v>0.2323248983137859</v>
+        <v>0.2323622649985839</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.06140623562012493</v>
+        <v>0.06074595351668277</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3807699459194911</v>
+        <v>0.382669945919491</v>
       </c>
       <c r="C95">
-        <v>-0.4733209324533213</v>
+        <v>-0.4873631329826698</v>
       </c>
       <c r="D95">
-        <v>0.5376090675466787</v>
+        <v>0.5345768670173302</v>
       </c>
       <c r="E95">
-        <v>0.98293</v>
+        <v>0.9939399999999999</v>
       </c>
       <c r="F95">
-        <v>1.02393</v>
+        <v>1.03494</v>
       </c>
       <c r="G95">
         <v>0.013</v>
@@ -9059,37 +9059,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M95">
-        <v>0.241442694</v>
+        <v>0.244038852</v>
       </c>
       <c r="N95">
-        <v>-0.2267760273333334</v>
+        <v>-0.2293721853333333</v>
       </c>
       <c r="O95">
-        <v>-0.05442624656</v>
+        <v>-0.05504932448</v>
       </c>
       <c r="P95">
-        <v>-0.1723497807733333</v>
+        <v>-0.1743228608533333</v>
       </c>
       <c r="Q95">
-        <v>-0.1643497807733333</v>
+        <v>-0.1663228608533333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.352471992440116</v>
+        <v>2.736917324513469</v>
       </c>
       <c r="T95">
-        <v>11.33353800796995</v>
+        <v>13.22246100929828</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01457902884400387</v>
+        <v>0.01442393279247191</v>
       </c>
       <c r="W95">
-        <v>0.2323622649985839</v>
+        <v>0.2323988366475351</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.06074595351668277</v>
+        <v>0.06009971996863295</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.382669945919491</v>
+        <v>0.3845699459194911</v>
       </c>
       <c r="C96">
-        <v>-0.4873631329826698</v>
+        <v>-0.5013713211618962</v>
       </c>
       <c r="D96">
-        <v>0.5345768670173302</v>
+        <v>0.5315786788381039</v>
       </c>
       <c r="E96">
-        <v>0.9939399999999999</v>
+        <v>1.00495</v>
       </c>
       <c r="F96">
-        <v>1.03494</v>
+        <v>1.04595</v>
       </c>
       <c r="G96">
         <v>0.013</v>
@@ -9141,37 +9141,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M96">
-        <v>0.244038852</v>
+        <v>0.24663501</v>
       </c>
       <c r="N96">
-        <v>-0.2293721853333333</v>
+        <v>-0.2319683433333334</v>
       </c>
       <c r="O96">
-        <v>-0.05504932448</v>
+        <v>-0.05567240240000001</v>
       </c>
       <c r="P96">
-        <v>-0.1743228608533333</v>
+        <v>-0.1762959409333334</v>
       </c>
       <c r="Q96">
-        <v>-0.1663228608533333</v>
+        <v>-0.1682959409333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.736917324513469</v>
+        <v>3.275140789416165</v>
       </c>
       <c r="T96">
-        <v>13.22246100929828</v>
+        <v>15.86695321115794</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01442393279247191</v>
+        <v>0.01427210192097221</v>
       </c>
       <c r="W96">
-        <v>0.2323988366475351</v>
+        <v>0.2324346383670348</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.06009971996863295</v>
+        <v>0.05946709133738415</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3845699459194911</v>
+        <v>0.386469945919491</v>
       </c>
       <c r="C97">
-        <v>-0.5013713211618962</v>
+        <v>-0.5153460660767031</v>
       </c>
       <c r="D97">
-        <v>0.5315786788381039</v>
+        <v>0.528613933923297</v>
       </c>
       <c r="E97">
-        <v>1.00495</v>
+        <v>1.01596</v>
       </c>
       <c r="F97">
-        <v>1.04595</v>
+        <v>1.05696</v>
       </c>
       <c r="G97">
         <v>0.013</v>
@@ -9223,37 +9223,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M97">
-        <v>0.24663501</v>
+        <v>0.249231168</v>
       </c>
       <c r="N97">
-        <v>-0.2319683433333334</v>
+        <v>-0.2345645013333334</v>
       </c>
       <c r="O97">
-        <v>-0.05567240240000001</v>
+        <v>-0.05629548032000001</v>
       </c>
       <c r="P97">
-        <v>-0.1762959409333334</v>
+        <v>-0.1782690210133334</v>
       </c>
       <c r="Q97">
-        <v>-0.1682959409333334</v>
+        <v>-0.1702690210133334</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.275140789416165</v>
+        <v>4.082475986770208</v>
       </c>
       <c r="T97">
-        <v>15.86695321115794</v>
+        <v>19.83369151394744</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01427210192097221</v>
+        <v>0.01412343419262875</v>
       </c>
       <c r="W97">
-        <v>0.2324346383670348</v>
+        <v>0.2324696942173781</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.05946709133738415</v>
+        <v>0.05884764246928642</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.386469945919491</v>
+        <v>0.388369945919491</v>
       </c>
       <c r="C98">
-        <v>-0.5153460660767029</v>
+        <v>-0.5292879241874849</v>
       </c>
       <c r="D98">
-        <v>0.528613933923297</v>
+        <v>0.5256820758125149</v>
       </c>
       <c r="E98">
-        <v>1.01596</v>
+        <v>1.02697</v>
       </c>
       <c r="F98">
-        <v>1.05696</v>
+        <v>1.06797</v>
       </c>
       <c r="G98">
         <v>0.013</v>
@@ -9305,37 +9305,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M98">
-        <v>0.249231168</v>
+        <v>0.251827326</v>
       </c>
       <c r="N98">
-        <v>-0.2345645013333333</v>
+        <v>-0.2371606593333333</v>
       </c>
       <c r="O98">
-        <v>-0.05629548031999999</v>
+        <v>-0.05691855823999999</v>
       </c>
       <c r="P98">
-        <v>-0.1782690210133333</v>
+        <v>-0.1802421010933333</v>
       </c>
       <c r="Q98">
-        <v>-0.1702690210133333</v>
+        <v>-0.1722421010933333</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>4.082475986770197</v>
+        <v>5.428034649026928</v>
       </c>
       <c r="T98">
-        <v>19.83369151394738</v>
+        <v>26.44492201859651</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01412343419262875</v>
+        <v>0.01397783177827175</v>
       </c>
       <c r="W98">
-        <v>0.2324696942173781</v>
+        <v>0.2325040272666835</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.05884764246928642</v>
+        <v>0.05824096574279891</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.388369945919491</v>
+        <v>0.390269945919491</v>
       </c>
       <c r="C99">
-        <v>-0.5292879241874849</v>
+        <v>-0.5431974396775164</v>
       </c>
       <c r="D99">
-        <v>0.5256820758125149</v>
+        <v>0.5227825603224836</v>
       </c>
       <c r="E99">
-        <v>1.02697</v>
+        <v>1.03798</v>
       </c>
       <c r="F99">
-        <v>1.06797</v>
+        <v>1.07898</v>
       </c>
       <c r="G99">
         <v>0.013</v>
@@ -9387,37 +9387,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M99">
-        <v>0.251827326</v>
+        <v>0.254423484</v>
       </c>
       <c r="N99">
-        <v>-0.2371606593333333</v>
+        <v>-0.2397568173333334</v>
       </c>
       <c r="O99">
-        <v>-0.05691855823999999</v>
+        <v>-0.05754163616000001</v>
       </c>
       <c r="P99">
-        <v>-0.1802421010933333</v>
+        <v>-0.1822151811733334</v>
       </c>
       <c r="Q99">
-        <v>-0.1722421010933333</v>
+        <v>-0.1742151811733333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>5.428034649026928</v>
+        <v>8.119151973540394</v>
       </c>
       <c r="T99">
-        <v>26.44492201859651</v>
+        <v>39.66738302789476</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01397783177827175</v>
+        <v>0.01383520084175877</v>
       </c>
       <c r="W99">
-        <v>0.2325040272666835</v>
+        <v>0.2325376596415133</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.05824096574279891</v>
+        <v>0.05764667017399483</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.390269945919491</v>
+        <v>0.3921699459194911</v>
       </c>
       <c r="C100">
-        <v>-0.5431974396775164</v>
+        <v>-0.5570751447896788</v>
       </c>
       <c r="D100">
-        <v>0.5227825603224836</v>
+        <v>0.5199148552103212</v>
       </c>
       <c r="E100">
-        <v>1.03798</v>
+        <v>1.04899</v>
       </c>
       <c r="F100">
-        <v>1.07898</v>
+        <v>1.08999</v>
       </c>
       <c r="G100">
         <v>0.013</v>
@@ -9469,37 +9469,37 @@
         <v>0.01466666666666667</v>
       </c>
       <c r="M100">
-        <v>0.254423484</v>
+        <v>0.257019642</v>
       </c>
       <c r="N100">
-        <v>-0.2397568173333334</v>
+        <v>-0.2423529753333333</v>
       </c>
       <c r="O100">
-        <v>-0.05754163616000001</v>
+        <v>-0.05816471408</v>
       </c>
       <c r="P100">
-        <v>-0.1822151811733334</v>
+        <v>-0.1841882612533333</v>
       </c>
       <c r="Q100">
-        <v>-0.1742151811733333</v>
+        <v>-0.1761882612533333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>8.119151973540394</v>
+        <v>16.19250394708079</v>
       </c>
       <c r="T100">
-        <v>39.66738302789476</v>
+        <v>79.33476605578953</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01383520084175877</v>
+        <v>0.01369545133830666</v>
       </c>
       <c r="W100">
-        <v>0.2325376596415133</v>
+        <v>0.2325706125744273</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.05764667017399483</v>
+        <v>0.05706438057627772</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3921699459194911</v>
-      </c>
-      <c r="C101">
-        <v>-0.5570751447896788</v>
-      </c>
-      <c r="D101">
-        <v>0.5199148552103212</v>
-      </c>
-      <c r="E101">
-        <v>1.04899</v>
-      </c>
-      <c r="F101">
-        <v>1.08999</v>
-      </c>
-      <c r="G101">
-        <v>0.013</v>
-      </c>
-      <c r="H101">
-        <v>1.06</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.02266666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.008000000000000002</v>
-      </c>
-      <c r="L101">
-        <v>0.01466666666666667</v>
-      </c>
-      <c r="M101">
-        <v>0.257019642</v>
-      </c>
-      <c r="N101">
-        <v>-0.2423529753333333</v>
-      </c>
-      <c r="O101">
-        <v>-0.05816471408</v>
-      </c>
-      <c r="P101">
-        <v>-0.1841882612533333</v>
-      </c>
-      <c r="Q101">
-        <v>-0.1761882612533333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>16.19250394708079</v>
-      </c>
-      <c r="T101">
-        <v>79.33476605578953</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01369545133830666</v>
-      </c>
-      <c r="W101">
-        <v>0.2325706125744273</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.05706438057627772</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
